--- a/research/traditional_assets/database/data/sweden/sweden_chemical_basic.xlsx
+++ b/research/traditional_assets/database/data/sweden/sweden_chemical_basic.xlsx
@@ -1909,7 +1909,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -2046,22 +2046,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.08500419409238885</v>
+        <v>0.08486481545255853</v>
       </c>
       <c r="C2">
-        <v>80.26291699776004</v>
+        <v>79.53639137581857</v>
       </c>
       <c r="D2">
-        <v>74.30291699776005</v>
+        <v>74.40239137581857</v>
       </c>
       <c r="E2">
-        <v>-20.6</v>
+        <v>-19.774</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>0.826</v>
       </c>
       <c r="G2">
         <v>5.96</v>
@@ -2082,28 +2082,28 @@
         <v>4.824999999999999</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>0.0415478</v>
       </c>
       <c r="N2">
-        <v>4.824999999999999</v>
+        <v>4.783452199999999</v>
       </c>
       <c r="O2">
-        <v>0.9939499999999999</v>
+        <v>0.9853911531999999</v>
       </c>
       <c r="P2">
-        <v>3.831049999999999</v>
+        <v>3.798061046799999</v>
       </c>
       <c r="Q2">
-        <v>13.13105</v>
+        <v>13.0980610468</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.08500419409238885</v>
+        <v>0.08531861964904902</v>
       </c>
       <c r="T2">
-        <v>0.9054086395470866</v>
+        <v>0.9126701997470905</v>
       </c>
       <c r="U2">
         <v>0.0503</v>
@@ -2120,7 +2120,7 @@
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>116.1312993708451</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -2128,22 +2128,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.08486481545255853</v>
+        <v>0.08472543681272821</v>
       </c>
       <c r="C3">
-        <v>79.53639137581857</v>
+        <v>78.81013245718736</v>
       </c>
       <c r="D3">
-        <v>74.40239137581857</v>
+        <v>74.50213245718737</v>
       </c>
       <c r="E3">
-        <v>-19.774</v>
+        <v>-18.948</v>
       </c>
       <c r="F3">
-        <v>0.826</v>
+        <v>1.652</v>
       </c>
       <c r="G3">
         <v>5.96</v>
@@ -2164,28 +2164,28 @@
         <v>4.824999999999999</v>
       </c>
       <c r="M3">
-        <v>0.0415478</v>
+        <v>0.08309559999999999</v>
       </c>
       <c r="N3">
-        <v>4.783452199999999</v>
+        <v>4.741904399999999</v>
       </c>
       <c r="O3">
-        <v>0.9853911531999999</v>
+        <v>0.9768323064</v>
       </c>
       <c r="P3">
-        <v>3.798061046799999</v>
+        <v>3.765072093599999</v>
       </c>
       <c r="Q3">
-        <v>13.0980610468</v>
+        <v>13.0650720936</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.08531861964904902</v>
+        <v>0.08563946205380429</v>
       </c>
       <c r="T3">
-        <v>0.9126701997470905</v>
+        <v>0.9200799550532168</v>
       </c>
       <c r="U3">
         <v>0.0503</v>
@@ -2202,7 +2202,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>116.1312993708451</v>
+        <v>58.06564968542257</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -2210,22 +2210,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.08472543681272821</v>
+        <v>0.08458605817289788</v>
       </c>
       <c r="C4">
-        <v>78.81013245718736</v>
+        <v>78.08414131590389</v>
       </c>
       <c r="D4">
-        <v>74.50213245718737</v>
+        <v>74.60214131590389</v>
       </c>
       <c r="E4">
-        <v>-18.948</v>
+        <v>-18.122</v>
       </c>
       <c r="F4">
-        <v>1.652</v>
+        <v>2.478</v>
       </c>
       <c r="G4">
         <v>5.96</v>
@@ -2246,28 +2246,28 @@
         <v>4.824999999999999</v>
       </c>
       <c r="M4">
-        <v>0.08309559999999999</v>
+        <v>0.1246434</v>
       </c>
       <c r="N4">
-        <v>4.741904399999999</v>
+        <v>4.700356599999999</v>
       </c>
       <c r="O4">
-        <v>0.9768323064</v>
+        <v>0.9682734595999999</v>
       </c>
       <c r="P4">
-        <v>3.765072093599999</v>
+        <v>3.732083140399999</v>
       </c>
       <c r="Q4">
-        <v>13.0650720936</v>
+        <v>13.0320831404</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.08563946205380429</v>
+        <v>0.08596691976587412</v>
       </c>
       <c r="T4">
-        <v>0.9200799550532168</v>
+        <v>0.9276424888192635</v>
       </c>
       <c r="U4">
         <v>0.0503</v>
@@ -2284,7 +2284,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>58.06564968542257</v>
+        <v>38.71043312361505</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -2292,22 +2292,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.08458605817289788</v>
+        <v>0.08444667953306757</v>
       </c>
       <c r="C5">
-        <v>78.08414131590389</v>
+        <v>77.35841903178034</v>
       </c>
       <c r="D5">
-        <v>74.60214131590389</v>
+        <v>74.70241903178035</v>
       </c>
       <c r="E5">
-        <v>-18.122</v>
+        <v>-17.296</v>
       </c>
       <c r="F5">
-        <v>2.478</v>
+        <v>3.304</v>
       </c>
       <c r="G5">
         <v>5.96</v>
@@ -2328,28 +2328,28 @@
         <v>4.824999999999999</v>
       </c>
       <c r="M5">
-        <v>0.1246434</v>
+        <v>0.1661912</v>
       </c>
       <c r="N5">
-        <v>4.700356599999999</v>
+        <v>4.658808799999999</v>
       </c>
       <c r="O5">
-        <v>0.9682734595999999</v>
+        <v>0.9597146127999999</v>
       </c>
       <c r="P5">
-        <v>3.732083140399999</v>
+        <v>3.699094187199999</v>
       </c>
       <c r="Q5">
-        <v>13.0320831404</v>
+        <v>12.9990941872</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.08596691976587412</v>
+        <v>0.08630119951361205</v>
       </c>
       <c r="T5">
-        <v>0.9276424888192635</v>
+        <v>0.9353625753721028</v>
       </c>
       <c r="U5">
         <v>0.0503</v>
@@ -2366,7 +2366,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>38.71043312361505</v>
+        <v>29.03282484271129</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -2374,22 +2374,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.08444667953306757</v>
+        <v>0.08430730089323725</v>
       </c>
       <c r="C6">
-        <v>77.35841903178034</v>
+        <v>76.63296669044254</v>
       </c>
       <c r="D6">
-        <v>74.70241903178035</v>
+        <v>74.80296669044255</v>
       </c>
       <c r="E6">
-        <v>-17.296</v>
+        <v>-16.47</v>
       </c>
       <c r="F6">
-        <v>3.304</v>
+        <v>4.13</v>
       </c>
       <c r="G6">
         <v>5.96</v>
@@ -2410,28 +2410,28 @@
         <v>4.824999999999999</v>
       </c>
       <c r="M6">
-        <v>0.1661912</v>
+        <v>0.207739</v>
       </c>
       <c r="N6">
-        <v>4.658808799999999</v>
+        <v>4.617260999999999</v>
       </c>
       <c r="O6">
-        <v>0.9597146127999999</v>
+        <v>0.951155766</v>
       </c>
       <c r="P6">
-        <v>3.699094187199999</v>
+        <v>3.666105233999999</v>
       </c>
       <c r="Q6">
-        <v>12.9990941872</v>
+        <v>12.966105234</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.08630119951361205</v>
+        <v>0.08664251672972342</v>
       </c>
       <c r="T6">
-        <v>0.9353625753721028</v>
+        <v>0.9432451900628965</v>
       </c>
       <c r="U6">
         <v>0.0503</v>
@@ -2448,7 +2448,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>29.03282484271129</v>
+        <v>23.22625987416903</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -2456,22 +2456,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.08430730089323725</v>
+        <v>0.08416792225340691</v>
       </c>
       <c r="C7">
-        <v>76.63296669044254</v>
+        <v>75.90778538336907</v>
       </c>
       <c r="D7">
-        <v>74.80296669044255</v>
+        <v>74.90378538336908</v>
       </c>
       <c r="E7">
-        <v>-16.47</v>
+        <v>-15.644</v>
       </c>
       <c r="F7">
-        <v>4.13</v>
+        <v>4.956</v>
       </c>
       <c r="G7">
         <v>5.96</v>
@@ -2492,28 +2492,28 @@
         <v>4.824999999999999</v>
       </c>
       <c r="M7">
-        <v>0.207739</v>
+        <v>0.2492868</v>
       </c>
       <c r="N7">
-        <v>4.617260999999999</v>
+        <v>4.575713199999999</v>
       </c>
       <c r="O7">
-        <v>0.951155766</v>
+        <v>0.9425969191999999</v>
       </c>
       <c r="P7">
-        <v>3.666105233999999</v>
+        <v>3.633116280799999</v>
       </c>
       <c r="Q7">
-        <v>12.966105234</v>
+        <v>12.9331162808</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.08664251672972342</v>
+        <v>0.08699109601426268</v>
       </c>
       <c r="T7">
-        <v>0.9432451900628965</v>
+        <v>0.9512955199598772</v>
       </c>
       <c r="U7">
         <v>0.0503</v>
@@ -2530,7 +2530,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>23.22625987416903</v>
+        <v>19.35521656180752</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -2538,22 +2538,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.08416792225340691</v>
+        <v>0.0840285436135766</v>
       </c>
       <c r="C8">
-        <v>75.90778538336907</v>
+        <v>75.18287620793078</v>
       </c>
       <c r="D8">
-        <v>74.90378538336908</v>
+        <v>75.00487620793078</v>
       </c>
       <c r="E8">
-        <v>-15.644</v>
+        <v>-14.818</v>
       </c>
       <c r="F8">
-        <v>4.956</v>
+        <v>5.781999999999999</v>
       </c>
       <c r="G8">
         <v>5.96</v>
@@ -2574,28 +2574,28 @@
         <v>4.824999999999999</v>
       </c>
       <c r="M8">
-        <v>0.2492868</v>
+        <v>0.2908345999999999</v>
       </c>
       <c r="N8">
-        <v>4.575713199999999</v>
+        <v>4.534165399999999</v>
       </c>
       <c r="O8">
-        <v>0.9425969191999999</v>
+        <v>0.9340380723999999</v>
       </c>
       <c r="P8">
-        <v>3.633116280799999</v>
+        <v>3.600127327599999</v>
       </c>
       <c r="Q8">
-        <v>12.9331162808</v>
+        <v>12.9001273276</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.08699109601426268</v>
+        <v>0.08734717162750172</v>
       </c>
       <c r="T8">
-        <v>0.9512955199598772</v>
+        <v>0.9595189752309866</v>
       </c>
       <c r="U8">
         <v>0.0503</v>
@@ -2612,7 +2612,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>19.35521656180752</v>
+        <v>16.59018562440645</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -2620,22 +2620,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.08402854361357659</v>
+        <v>0.08388916497374628</v>
       </c>
       <c r="C9">
-        <v>75.18287620793079</v>
+        <v>74.45824026743063</v>
       </c>
       <c r="D9">
-        <v>75.00487620793079</v>
+        <v>75.10624026743064</v>
       </c>
       <c r="E9">
-        <v>-14.818</v>
+        <v>-13.992</v>
       </c>
       <c r="F9">
-        <v>5.782</v>
+        <v>6.608</v>
       </c>
       <c r="G9">
         <v>5.96</v>
@@ -2656,28 +2656,28 @@
         <v>4.824999999999999</v>
       </c>
       <c r="M9">
-        <v>0.2908346</v>
+        <v>0.3323824</v>
       </c>
       <c r="N9">
-        <v>4.534165399999999</v>
+        <v>4.492617599999999</v>
       </c>
       <c r="O9">
-        <v>0.9340380723999999</v>
+        <v>0.9254792255999998</v>
       </c>
       <c r="P9">
-        <v>3.600127327599999</v>
+        <v>3.567138374399999</v>
       </c>
       <c r="Q9">
-        <v>12.9001273276</v>
+        <v>12.8671383744</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.08734717162750172</v>
+        <v>0.08771098801494161</v>
       </c>
       <c r="T9">
-        <v>0.9595189752309866</v>
+        <v>0.9679212012688594</v>
       </c>
       <c r="U9">
         <v>0.0503</v>
@@ -2694,7 +2694,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>16.59018562440644</v>
+        <v>14.51641242135564</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2702,22 +2702,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.08388916497374628</v>
+        <v>0.08374978633391597</v>
       </c>
       <c r="C10">
-        <v>74.45824026743063</v>
+        <v>73.73387867114383</v>
       </c>
       <c r="D10">
-        <v>75.10624026743064</v>
+        <v>75.20787867114383</v>
       </c>
       <c r="E10">
-        <v>-13.992</v>
+        <v>-13.166</v>
       </c>
       <c r="F10">
-        <v>6.608</v>
+        <v>7.433999999999999</v>
       </c>
       <c r="G10">
         <v>5.96</v>
@@ -2738,28 +2738,28 @@
         <v>4.824999999999999</v>
       </c>
       <c r="M10">
-        <v>0.3323824</v>
+        <v>0.3739301999999999</v>
       </c>
       <c r="N10">
-        <v>4.492617599999999</v>
+        <v>4.451069799999999</v>
       </c>
       <c r="O10">
-        <v>0.9254792255999998</v>
+        <v>0.9169203787999999</v>
       </c>
       <c r="P10">
-        <v>3.567138374399999</v>
+        <v>3.534149421199999</v>
       </c>
       <c r="Q10">
-        <v>12.8671383744</v>
+        <v>12.8341494212</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.08771098801494161</v>
+        <v>0.08808280036694062</v>
       </c>
       <c r="T10">
-        <v>0.9679212012688594</v>
+        <v>0.9765080916152568</v>
       </c>
       <c r="U10">
         <v>0.0503</v>
@@ -2776,7 +2776,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>14.51641242135564</v>
+        <v>12.90347770787168</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2784,22 +2784,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.08374978633391597</v>
+        <v>0.08372950769408566</v>
       </c>
       <c r="C11">
-        <v>73.73387867114383</v>
+        <v>72.92268929215683</v>
       </c>
       <c r="D11">
-        <v>75.20787867114383</v>
+        <v>75.22268929215684</v>
       </c>
       <c r="E11">
-        <v>-13.166</v>
+        <v>-12.34</v>
       </c>
       <c r="F11">
-        <v>7.433999999999999</v>
+        <v>8.259999999999998</v>
       </c>
       <c r="G11">
         <v>5.96</v>
@@ -2820,45 +2820,45 @@
         <v>4.824999999999999</v>
       </c>
       <c r="M11">
-        <v>0.3739301999999999</v>
+        <v>0.4278679999999999</v>
       </c>
       <c r="N11">
-        <v>4.451069799999999</v>
+        <v>4.397131999999999</v>
       </c>
       <c r="O11">
-        <v>0.9169203787999999</v>
+        <v>0.9058091919999999</v>
       </c>
       <c r="P11">
-        <v>3.534149421199999</v>
+        <v>3.491322807999999</v>
       </c>
       <c r="Q11">
-        <v>12.8341494212</v>
+        <v>12.791322808</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.08808280036694062</v>
+        <v>0.08846287521565072</v>
       </c>
       <c r="T11">
-        <v>0.9765080916152568</v>
+        <v>0.9852858017471295</v>
       </c>
       <c r="U11">
-        <v>0.0503</v>
+        <v>0.0518</v>
       </c>
       <c r="V11">
         <v>0.206</v>
       </c>
       <c r="W11">
-        <v>0.0399382</v>
+        <v>0.0411292</v>
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y11">
-        <v>12.90347770787168</v>
+        <v>11.27684239064384</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2866,22 +2866,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.08372950769408566</v>
+        <v>0.08360203905425533</v>
       </c>
       <c r="C12">
-        <v>72.92268929215683</v>
+        <v>72.18992048655613</v>
       </c>
       <c r="D12">
-        <v>75.22268929215684</v>
+        <v>75.31592048655614</v>
       </c>
       <c r="E12">
-        <v>-12.34</v>
+        <v>-11.514</v>
       </c>
       <c r="F12">
-        <v>8.26</v>
+        <v>9.086</v>
       </c>
       <c r="G12">
         <v>5.96</v>
@@ -2902,28 +2902,28 @@
         <v>4.824999999999999</v>
       </c>
       <c r="M12">
-        <v>0.427868</v>
+        <v>0.4706548</v>
       </c>
       <c r="N12">
-        <v>4.397131999999999</v>
+        <v>4.354345199999999</v>
       </c>
       <c r="O12">
-        <v>0.9058091919999999</v>
+        <v>0.8969951111999999</v>
       </c>
       <c r="P12">
-        <v>3.491322807999999</v>
+        <v>3.457350088799999</v>
       </c>
       <c r="Q12">
-        <v>12.791322808</v>
+        <v>12.7573500888</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.08846287521565072</v>
+        <v>0.08885149107219699</v>
       </c>
       <c r="T12">
-        <v>0.9852858017471295</v>
+        <v>0.9942607637920783</v>
       </c>
       <c r="U12">
         <v>0.0518</v>
@@ -2940,7 +2940,7 @@
         </is>
       </c>
       <c r="Y12">
-        <v>11.27684239064384</v>
+        <v>10.25167490058531</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2948,22 +2948,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.08360203905425533</v>
+        <v>0.083636546414425</v>
       </c>
       <c r="C13">
-        <v>72.18992048655613</v>
+        <v>71.33865882718433</v>
       </c>
       <c r="D13">
-        <v>75.31592048655614</v>
+        <v>75.29065882718433</v>
       </c>
       <c r="E13">
-        <v>-11.514</v>
+        <v>-10.688</v>
       </c>
       <c r="F13">
-        <v>9.086</v>
+        <v>9.911999999999999</v>
       </c>
       <c r="G13">
         <v>5.96</v>
@@ -2984,45 +2984,45 @@
         <v>4.824999999999999</v>
       </c>
       <c r="M13">
-        <v>0.4706548</v>
+        <v>0.530292</v>
       </c>
       <c r="N13">
-        <v>4.354345199999999</v>
+        <v>4.294707999999999</v>
       </c>
       <c r="O13">
-        <v>0.8969951111999999</v>
+        <v>0.8847098479999999</v>
       </c>
       <c r="P13">
-        <v>3.457350088799999</v>
+        <v>3.409998151999999</v>
       </c>
       <c r="Q13">
-        <v>12.7573500888</v>
+        <v>12.709998152</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.08885149107219699</v>
+        <v>0.08924893910730114</v>
       </c>
       <c r="T13">
-        <v>0.9942607637920783</v>
+        <v>1.003439702247139</v>
       </c>
       <c r="U13">
-        <v>0.0518</v>
+        <v>0.0535</v>
       </c>
       <c r="V13">
         <v>0.206</v>
       </c>
       <c r="W13">
-        <v>0.0411292</v>
+        <v>0.042479</v>
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y13">
-        <v>10.25167490058531</v>
+        <v>9.09876068279363</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -3030,22 +3030,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.083636546414425</v>
+        <v>0.08352257577459467</v>
       </c>
       <c r="C14">
-        <v>71.33865882718433</v>
+        <v>70.59615735263819</v>
       </c>
       <c r="D14">
-        <v>75.29065882718433</v>
+        <v>75.37415735263819</v>
       </c>
       <c r="E14">
-        <v>-10.688</v>
+        <v>-9.862000000000002</v>
       </c>
       <c r="F14">
-        <v>9.911999999999999</v>
+        <v>10.738</v>
       </c>
       <c r="G14">
         <v>5.96</v>
@@ -3066,28 +3066,28 @@
         <v>4.824999999999999</v>
       </c>
       <c r="M14">
-        <v>0.530292</v>
+        <v>0.574483</v>
       </c>
       <c r="N14">
-        <v>4.294707999999999</v>
+        <v>4.250516999999999</v>
       </c>
       <c r="O14">
-        <v>0.8847098479999999</v>
+        <v>0.875606502</v>
       </c>
       <c r="P14">
-        <v>3.409998151999999</v>
+        <v>3.374910497999999</v>
       </c>
       <c r="Q14">
-        <v>12.709998152</v>
+        <v>12.674910498</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.08924893910730114</v>
+        <v>0.08965552387884446</v>
       </c>
       <c r="T14">
-        <v>1.003439702247139</v>
+        <v>1.012829650781627</v>
       </c>
       <c r="U14">
         <v>0.0535</v>
@@ -3104,7 +3104,7 @@
         </is>
       </c>
       <c r="Y14">
-        <v>9.09876068279363</v>
+        <v>8.398856014886427</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -3112,22 +3112,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.08352257577459467</v>
+        <v>0.08340860513476435</v>
       </c>
       <c r="C15">
-        <v>70.59615735263819</v>
+        <v>69.85384128606984</v>
       </c>
       <c r="D15">
-        <v>75.37415735263819</v>
+        <v>75.45784128606984</v>
       </c>
       <c r="E15">
-        <v>-9.862000000000002</v>
+        <v>-9.036000000000001</v>
       </c>
       <c r="F15">
-        <v>10.738</v>
+        <v>11.564</v>
       </c>
       <c r="G15">
         <v>5.96</v>
@@ -3148,28 +3148,28 @@
         <v>4.824999999999999</v>
       </c>
       <c r="M15">
-        <v>0.574483</v>
+        <v>0.6186739999999999</v>
       </c>
       <c r="N15">
-        <v>4.250516999999999</v>
+        <v>4.206325999999999</v>
       </c>
       <c r="O15">
-        <v>0.875606502</v>
+        <v>0.8665031559999998</v>
       </c>
       <c r="P15">
-        <v>3.374910497999999</v>
+        <v>3.339822843999999</v>
       </c>
       <c r="Q15">
-        <v>12.674910498</v>
+        <v>12.639822844</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.08965552387884446</v>
+        <v>0.0900715641101911</v>
       </c>
       <c r="T15">
-        <v>1.012829650781627</v>
+        <v>1.022437970212266</v>
       </c>
       <c r="U15">
         <v>0.0535</v>
@@ -3186,7 +3186,7 @@
         </is>
       </c>
       <c r="Y15">
-        <v>8.398856014886427</v>
+        <v>7.798937728108825</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -3194,22 +3194,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.08340860513476435</v>
+        <v>0.08338991449493403</v>
       </c>
       <c r="C16">
-        <v>69.85384128606984</v>
+        <v>69.04158278966285</v>
       </c>
       <c r="D16">
-        <v>75.45784128606984</v>
+        <v>75.47158278966286</v>
       </c>
       <c r="E16">
-        <v>-9.036000000000001</v>
+        <v>-8.210000000000001</v>
       </c>
       <c r="F16">
-        <v>11.564</v>
+        <v>12.39</v>
       </c>
       <c r="G16">
         <v>5.96</v>
@@ -3230,45 +3230,45 @@
         <v>4.824999999999999</v>
       </c>
       <c r="M16">
-        <v>0.6186739999999999</v>
+        <v>0.6727770000000001</v>
       </c>
       <c r="N16">
-        <v>4.206325999999999</v>
+        <v>4.152222999999999</v>
       </c>
       <c r="O16">
-        <v>0.8665031559999998</v>
+        <v>0.8553579379999999</v>
       </c>
       <c r="P16">
-        <v>3.339822843999999</v>
+        <v>3.296865061999999</v>
       </c>
       <c r="Q16">
-        <v>12.639822844</v>
+        <v>12.596865062</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.0900715641101911</v>
+        <v>0.09049739352345181</v>
       </c>
       <c r="T16">
-        <v>1.022437970212266</v>
+        <v>1.032272367747155</v>
       </c>
       <c r="U16">
-        <v>0.0535</v>
+        <v>0.0543</v>
       </c>
       <c r="V16">
         <v>0.206</v>
       </c>
       <c r="W16">
-        <v>0.042479</v>
+        <v>0.04311420000000001</v>
       </c>
       <c r="X16" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y16">
-        <v>7.798937728108825</v>
+        <v>7.171767168021497</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -3276,22 +3276,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.08338991449493403</v>
+        <v>0.0832822958551037</v>
       </c>
       <c r="C17">
-        <v>69.04158278966285</v>
+        <v>68.2948023248623</v>
       </c>
       <c r="D17">
-        <v>75.47158278966286</v>
+        <v>75.5508023248623</v>
       </c>
       <c r="E17">
-        <v>-8.210000000000003</v>
+        <v>-7.384000000000002</v>
       </c>
       <c r="F17">
-        <v>12.39</v>
+        <v>13.216</v>
       </c>
       <c r="G17">
         <v>5.96</v>
@@ -3312,28 +3312,28 @@
         <v>4.824999999999999</v>
       </c>
       <c r="M17">
-        <v>0.672777</v>
+        <v>0.7176288</v>
       </c>
       <c r="N17">
-        <v>4.152222999999999</v>
+        <v>4.107371199999999</v>
       </c>
       <c r="O17">
-        <v>0.8553579379999999</v>
+        <v>0.8461184671999999</v>
       </c>
       <c r="P17">
-        <v>3.296865061999999</v>
+        <v>3.261252732799999</v>
       </c>
       <c r="Q17">
-        <v>12.596865062</v>
+        <v>12.5612527328</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.09049739352345181</v>
+        <v>0.09093336173226632</v>
       </c>
       <c r="T17">
-        <v>1.032272367747155</v>
+        <v>1.042340917604303</v>
       </c>
       <c r="U17">
         <v>0.0543</v>
@@ -3350,7 +3350,7 @@
         </is>
       </c>
       <c r="Y17">
-        <v>7.171767168021498</v>
+        <v>6.723531720020155</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -3358,22 +3358,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.0832822958551037</v>
+        <v>0.0831746772152734</v>
       </c>
       <c r="C18">
-        <v>68.2948023248623</v>
+        <v>67.54818834203645</v>
       </c>
       <c r="D18">
-        <v>75.5508023248623</v>
+        <v>75.63018834203646</v>
       </c>
       <c r="E18">
-        <v>-7.384000000000002</v>
+        <v>-6.558000000000002</v>
       </c>
       <c r="F18">
-        <v>13.216</v>
+        <v>14.042</v>
       </c>
       <c r="G18">
         <v>5.96</v>
@@ -3394,28 +3394,28 @@
         <v>4.824999999999999</v>
       </c>
       <c r="M18">
-        <v>0.7176288</v>
+        <v>0.7624806</v>
       </c>
       <c r="N18">
-        <v>4.107371199999999</v>
+        <v>4.062519399999999</v>
       </c>
       <c r="O18">
-        <v>0.8461184671999999</v>
+        <v>0.8368789964</v>
       </c>
       <c r="P18">
-        <v>3.261252732799999</v>
+        <v>3.225640403599999</v>
       </c>
       <c r="Q18">
-        <v>12.5612527328</v>
+        <v>12.5256404036</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.09093336173226632</v>
+        <v>0.09137983519912457</v>
       </c>
       <c r="T18">
-        <v>1.042340917604303</v>
+        <v>1.05265208312066</v>
       </c>
       <c r="U18">
         <v>0.0543</v>
@@ -3432,7 +3432,7 @@
         </is>
       </c>
       <c r="Y18">
-        <v>6.723531720020155</v>
+        <v>6.328029854136616</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -3440,22 +3440,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.0831746772152734</v>
+        <v>0.08320997857544307</v>
       </c>
       <c r="C19">
-        <v>67.54818834203645</v>
+        <v>66.69612954334011</v>
       </c>
       <c r="D19">
-        <v>75.63018834203646</v>
+        <v>75.60412954334011</v>
       </c>
       <c r="E19">
-        <v>-6.558000000000002</v>
+        <v>-5.732000000000001</v>
       </c>
       <c r="F19">
-        <v>14.042</v>
+        <v>14.868</v>
       </c>
       <c r="G19">
         <v>5.96</v>
@@ -3476,45 +3476,45 @@
         <v>4.824999999999999</v>
       </c>
       <c r="M19">
-        <v>0.7624806</v>
+        <v>0.8222004000000001</v>
       </c>
       <c r="N19">
-        <v>4.062519399999999</v>
+        <v>4.002799599999999</v>
       </c>
       <c r="O19">
-        <v>0.8368789964</v>
+        <v>0.8245767176</v>
       </c>
       <c r="P19">
-        <v>3.225640403599999</v>
+        <v>3.1782228824</v>
       </c>
       <c r="Q19">
-        <v>12.5256404036</v>
+        <v>12.4782228824</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.09137983519912457</v>
+        <v>0.09183719826273545</v>
       </c>
       <c r="T19">
-        <v>1.05265208312066</v>
+        <v>1.063214740478879</v>
       </c>
       <c r="U19">
-        <v>0.0543</v>
+        <v>0.0553</v>
       </c>
       <c r="V19">
         <v>0.206</v>
       </c>
       <c r="W19">
-        <v>0.04311420000000001</v>
+        <v>0.0439082</v>
       </c>
       <c r="X19" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y19">
-        <v>6.328029854136616</v>
+        <v>5.868398993724643</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -3522,22 +3522,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.08320997857544307</v>
+        <v>0.08311029993561277</v>
       </c>
       <c r="C20">
-        <v>66.69612954334011</v>
+        <v>65.94375671590981</v>
       </c>
       <c r="D20">
-        <v>75.60412954334011</v>
+        <v>75.67775671590982</v>
       </c>
       <c r="E20">
-        <v>-5.732000000000003</v>
+        <v>-4.906000000000002</v>
       </c>
       <c r="F20">
-        <v>14.868</v>
+        <v>15.694</v>
       </c>
       <c r="G20">
         <v>5.96</v>
@@ -3558,28 +3558,28 @@
         <v>4.824999999999999</v>
       </c>
       <c r="M20">
-        <v>0.8222003999999999</v>
+        <v>0.8678781999999999</v>
       </c>
       <c r="N20">
-        <v>4.002799599999999</v>
+        <v>3.957121799999999</v>
       </c>
       <c r="O20">
-        <v>0.8245767176</v>
+        <v>0.8151670907999999</v>
       </c>
       <c r="P20">
-        <v>3.1782228824</v>
+        <v>3.141954709199999</v>
       </c>
       <c r="Q20">
-        <v>12.4782228824</v>
+        <v>12.4419547092</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.09183719826273545</v>
+        <v>0.09230585424149723</v>
       </c>
       <c r="T20">
-        <v>1.063214740478879</v>
+        <v>1.074038204191622</v>
       </c>
       <c r="U20">
         <v>0.0553</v>
@@ -3596,7 +3596,7 @@
         </is>
       </c>
       <c r="Y20">
-        <v>5.868398993724644</v>
+        <v>5.559535888791768</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -3604,22 +3604,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.08311029993561277</v>
+        <v>0.08301062129578243</v>
       </c>
       <c r="C21">
-        <v>65.94375671590981</v>
+        <v>65.19152743209095</v>
       </c>
       <c r="D21">
-        <v>75.67775671590982</v>
+        <v>75.75152743209095</v>
       </c>
       <c r="E21">
-        <v>-4.906000000000002</v>
+        <v>-4.080000000000002</v>
       </c>
       <c r="F21">
-        <v>15.694</v>
+        <v>16.52</v>
       </c>
       <c r="G21">
         <v>5.96</v>
@@ -3640,28 +3640,28 @@
         <v>4.824999999999999</v>
       </c>
       <c r="M21">
-        <v>0.8678781999999999</v>
+        <v>0.913556</v>
       </c>
       <c r="N21">
-        <v>3.957121799999999</v>
+        <v>3.911443999999999</v>
       </c>
       <c r="O21">
-        <v>0.8151670907999999</v>
+        <v>0.8057574639999999</v>
       </c>
       <c r="P21">
-        <v>3.141954709199999</v>
+        <v>3.105686535999999</v>
       </c>
       <c r="Q21">
-        <v>12.4419547092</v>
+        <v>12.405686536</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.09230585424149723</v>
+        <v>0.09278622661972805</v>
       </c>
       <c r="T21">
-        <v>1.074038204191622</v>
+        <v>1.085132254497183</v>
       </c>
       <c r="U21">
         <v>0.0553</v>
@@ -3678,7 +3678,7 @@
         </is>
       </c>
       <c r="Y21">
-        <v>5.559535888791768</v>
+        <v>5.281559094352179</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3686,22 +3686,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.08301062129578243</v>
+        <v>0.08291094265595211</v>
       </c>
       <c r="C22">
-        <v>65.19152743209095</v>
+        <v>64.43944211207221</v>
       </c>
       <c r="D22">
-        <v>75.75152743209095</v>
+        <v>75.82544211207222</v>
       </c>
       <c r="E22">
-        <v>-4.080000000000002</v>
+        <v>-3.254000000000001</v>
       </c>
       <c r="F22">
-        <v>16.52</v>
+        <v>17.346</v>
       </c>
       <c r="G22">
         <v>5.96</v>
@@ -3722,28 +3722,28 @@
         <v>4.824999999999999</v>
       </c>
       <c r="M22">
-        <v>0.913556</v>
+        <v>0.9592338</v>
       </c>
       <c r="N22">
-        <v>3.911443999999999</v>
+        <v>3.865766199999999</v>
       </c>
       <c r="O22">
-        <v>0.8057574639999999</v>
+        <v>0.7963478371999999</v>
       </c>
       <c r="P22">
-        <v>3.105686535999999</v>
+        <v>3.0694183628</v>
       </c>
       <c r="Q22">
-        <v>12.405686536</v>
+        <v>12.3694183628</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.09278622661972805</v>
+        <v>0.09327876032399002</v>
       </c>
       <c r="T22">
-        <v>1.085132254497183</v>
+        <v>1.096507166835797</v>
       </c>
       <c r="U22">
         <v>0.0553</v>
@@ -3760,7 +3760,7 @@
         </is>
       </c>
       <c r="Y22">
-        <v>5.281559094352179</v>
+        <v>5.030056280335408</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3768,22 +3768,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.08291094265595211</v>
+        <v>0.08281126401612179</v>
       </c>
       <c r="C23">
-        <v>64.43944211207221</v>
+        <v>63.68750117768403</v>
       </c>
       <c r="D23">
-        <v>75.82544211207222</v>
+        <v>75.89950117768403</v>
       </c>
       <c r="E23">
-        <v>-3.254000000000005</v>
+        <v>-2.428000000000001</v>
       </c>
       <c r="F23">
-        <v>17.346</v>
+        <v>18.172</v>
       </c>
       <c r="G23">
         <v>5.96</v>
@@ -3804,28 +3804,28 @@
         <v>4.824999999999999</v>
       </c>
       <c r="M23">
-        <v>0.9592337999999998</v>
+        <v>1.0049116</v>
       </c>
       <c r="N23">
-        <v>3.865766199999999</v>
+        <v>3.820088399999999</v>
       </c>
       <c r="O23">
-        <v>0.7963478371999999</v>
+        <v>0.7869382104</v>
       </c>
       <c r="P23">
-        <v>3.0694183628</v>
+        <v>3.0331501896</v>
       </c>
       <c r="Q23">
-        <v>12.3694183628</v>
+        <v>12.3331501896</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.09327876032399002</v>
+        <v>0.09378392309759204</v>
       </c>
       <c r="T23">
-        <v>1.096507166835797</v>
+        <v>1.108173743593349</v>
       </c>
       <c r="U23">
         <v>0.0553</v>
@@ -3842,7 +3842,7 @@
         </is>
       </c>
       <c r="Y23">
-        <v>5.03005628033541</v>
+        <v>4.801417358501981</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3850,22 +3850,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.08281126401612179</v>
+        <v>0.08271158537629147</v>
       </c>
       <c r="C24">
-        <v>63.68750117768403</v>
+        <v>62.93570505240632</v>
       </c>
       <c r="D24">
-        <v>75.89950117768403</v>
+        <v>75.97370505240633</v>
       </c>
       <c r="E24">
-        <v>-2.428000000000001</v>
+        <v>-1.602</v>
       </c>
       <c r="F24">
-        <v>18.172</v>
+        <v>18.998</v>
       </c>
       <c r="G24">
         <v>5.96</v>
@@ -3886,28 +3886,28 @@
         <v>4.824999999999999</v>
       </c>
       <c r="M24">
-        <v>1.0049116</v>
+        <v>1.0505894</v>
       </c>
       <c r="N24">
-        <v>3.820088399999999</v>
+        <v>3.7744106</v>
       </c>
       <c r="O24">
-        <v>0.7869382104</v>
+        <v>0.7775285836</v>
       </c>
       <c r="P24">
-        <v>3.0331501896</v>
+        <v>2.996882016399999</v>
       </c>
       <c r="Q24">
-        <v>12.3331501896</v>
+        <v>12.2968820164</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.09378392309759204</v>
+        <v>0.09430220698219671</v>
       </c>
       <c r="T24">
-        <v>1.108173743593349</v>
+        <v>1.120143348318631</v>
       </c>
       <c r="U24">
         <v>0.0553</v>
@@ -3924,7 +3924,7 @@
         </is>
       </c>
       <c r="Y24">
-        <v>4.801417358501981</v>
+        <v>4.592660082045374</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3932,22 +3932,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.08271158537629147</v>
+        <v>0.08308830673646117</v>
       </c>
       <c r="C25">
-        <v>62.93570505240632</v>
+        <v>61.83002120728945</v>
       </c>
       <c r="D25">
-        <v>75.97370505240633</v>
+        <v>75.69402120728945</v>
       </c>
       <c r="E25">
-        <v>-1.602</v>
+        <v>-0.7759999999999998</v>
       </c>
       <c r="F25">
-        <v>18.998</v>
+        <v>19.824</v>
       </c>
       <c r="G25">
         <v>5.96</v>
@@ -3968,45 +3968,45 @@
         <v>4.824999999999999</v>
       </c>
       <c r="M25">
-        <v>1.0505894</v>
+        <v>1.1458272</v>
       </c>
       <c r="N25">
-        <v>3.7744106</v>
+        <v>3.679172799999999</v>
       </c>
       <c r="O25">
-        <v>0.7775285836</v>
+        <v>0.7579095967999998</v>
       </c>
       <c r="P25">
-        <v>2.996882016399999</v>
+        <v>2.921263203199999</v>
       </c>
       <c r="Q25">
-        <v>12.2968820164</v>
+        <v>12.2212632032</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.09430220698219671</v>
+        <v>0.09483412991639625</v>
       </c>
       <c r="T25">
-        <v>1.120143348318631</v>
+        <v>1.132427942641946</v>
       </c>
       <c r="U25">
-        <v>0.0553</v>
+        <v>0.0578</v>
       </c>
       <c r="V25">
         <v>0.206</v>
       </c>
       <c r="W25">
-        <v>0.0439082</v>
+        <v>0.04589320000000001</v>
       </c>
       <c r="X25" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y25">
-        <v>4.592660082045374</v>
+        <v>4.210931630877674</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -4014,22 +4014,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.08308830673646116</v>
+        <v>0.08300847809663082</v>
       </c>
       <c r="C26">
-        <v>61.83002120728946</v>
+        <v>61.06311516216869</v>
       </c>
       <c r="D26">
-        <v>75.69402120728947</v>
+        <v>75.7531151621687</v>
       </c>
       <c r="E26">
-        <v>-0.7760000000000034</v>
+        <v>0.04999999999999716</v>
       </c>
       <c r="F26">
-        <v>19.824</v>
+        <v>20.65</v>
       </c>
       <c r="G26">
         <v>5.96</v>
@@ -4050,28 +4050,28 @@
         <v>4.824999999999999</v>
       </c>
       <c r="M26">
-        <v>1.1458272</v>
+        <v>1.19357</v>
       </c>
       <c r="N26">
-        <v>3.679172799999999</v>
+        <v>3.631429999999999</v>
       </c>
       <c r="O26">
-        <v>0.7579095967999998</v>
+        <v>0.7480745799999998</v>
       </c>
       <c r="P26">
-        <v>2.921263203199999</v>
+        <v>2.883355419999999</v>
       </c>
       <c r="Q26">
-        <v>12.2212632032</v>
+        <v>12.18335542</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.09483412991639625</v>
+        <v>0.09538023746217442</v>
       </c>
       <c r="T26">
-        <v>1.132427942641946</v>
+        <v>1.145040126147215</v>
       </c>
       <c r="U26">
         <v>0.0578</v>
@@ -4088,7 +4088,7 @@
         </is>
       </c>
       <c r="Y26">
-        <v>4.210931630877674</v>
+        <v>4.042494365642567</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -4096,22 +4096,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.08300847809663082</v>
+        <v>0.0836511894568005</v>
       </c>
       <c r="C27">
-        <v>61.06311516216869</v>
+        <v>59.76394427664107</v>
       </c>
       <c r="D27">
-        <v>75.7531151621687</v>
+        <v>75.27994427664107</v>
       </c>
       <c r="E27">
-        <v>0.04999999999999716</v>
+        <v>0.8759999999999977</v>
       </c>
       <c r="F27">
-        <v>20.65</v>
+        <v>21.476</v>
       </c>
       <c r="G27">
         <v>5.96</v>
@@ -4132,45 +4132,45 @@
         <v>4.824999999999999</v>
       </c>
       <c r="M27">
-        <v>1.19357</v>
+        <v>1.3164788</v>
       </c>
       <c r="N27">
-        <v>3.631429999999999</v>
+        <v>3.508521199999999</v>
       </c>
       <c r="O27">
-        <v>0.7480745799999998</v>
+        <v>0.7227553671999999</v>
       </c>
       <c r="P27">
-        <v>2.883355419999999</v>
+        <v>2.785765832799999</v>
       </c>
       <c r="Q27">
-        <v>12.18335542</v>
+        <v>12.0857658328</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.09538023746217442</v>
+        <v>0.09594110467135203</v>
       </c>
       <c r="T27">
-        <v>1.145040126147215</v>
+        <v>1.157993179476952</v>
       </c>
       <c r="U27">
-        <v>0.0578</v>
+        <v>0.0613</v>
       </c>
       <c r="V27">
         <v>0.206</v>
       </c>
       <c r="W27">
-        <v>0.04589320000000001</v>
+        <v>0.04867220000000001</v>
       </c>
       <c r="X27" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y27">
-        <v>4.042494365642567</v>
+        <v>3.665079908616834</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -4178,22 +4178,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.0836511894568005</v>
+        <v>0.08359915081697018</v>
       </c>
       <c r="C28">
-        <v>59.76394427664107</v>
+        <v>58.97603563521066</v>
       </c>
       <c r="D28">
-        <v>75.27994427664107</v>
+        <v>75.31803563521066</v>
       </c>
       <c r="E28">
-        <v>0.8759999999999977</v>
+        <v>1.701999999999998</v>
       </c>
       <c r="F28">
-        <v>21.476</v>
+        <v>22.302</v>
       </c>
       <c r="G28">
         <v>5.96</v>
@@ -4214,28 +4214,28 @@
         <v>4.824999999999999</v>
       </c>
       <c r="M28">
-        <v>1.3164788</v>
+        <v>1.3671126</v>
       </c>
       <c r="N28">
-        <v>3.508521199999999</v>
+        <v>3.457887399999999</v>
       </c>
       <c r="O28">
-        <v>0.7227553671999999</v>
+        <v>0.7123248043999999</v>
       </c>
       <c r="P28">
-        <v>2.785765832799999</v>
+        <v>2.745562595599999</v>
       </c>
       <c r="Q28">
-        <v>12.0857658328</v>
+        <v>12.0455625956</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.09594110467135203</v>
+        <v>0.09651733810543861</v>
       </c>
       <c r="T28">
-        <v>1.157993179476952</v>
+        <v>1.171301110980106</v>
       </c>
       <c r="U28">
         <v>0.0613</v>
@@ -4252,7 +4252,7 @@
         </is>
       </c>
       <c r="Y28">
-        <v>3.665079908616834</v>
+        <v>3.529336208297692</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -4260,22 +4260,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.08359915081697018</v>
+        <v>0.08416960817713985</v>
       </c>
       <c r="C29">
-        <v>58.97603563521066</v>
+        <v>57.7345642569467</v>
       </c>
       <c r="D29">
-        <v>75.31803563521066</v>
+        <v>74.9025642569467</v>
       </c>
       <c r="E29">
-        <v>1.701999999999998</v>
+        <v>2.527999999999999</v>
       </c>
       <c r="F29">
-        <v>22.302</v>
+        <v>23.128</v>
       </c>
       <c r="G29">
         <v>5.96</v>
@@ -4296,45 +4296,45 @@
         <v>4.824999999999999</v>
       </c>
       <c r="M29">
-        <v>1.3671126</v>
+        <v>1.4825048</v>
       </c>
       <c r="N29">
-        <v>3.457887399999999</v>
+        <v>3.342495199999999</v>
       </c>
       <c r="O29">
-        <v>0.7123248043999999</v>
+        <v>0.6885540111999999</v>
       </c>
       <c r="P29">
-        <v>2.745562595599999</v>
+        <v>2.653941188799999</v>
       </c>
       <c r="Q29">
-        <v>12.0455625956</v>
+        <v>11.9539411888</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.09651733810543861</v>
+        <v>0.09710957802380536</v>
       </c>
       <c r="T29">
-        <v>1.171301110980106</v>
+        <v>1.184978707247237</v>
       </c>
       <c r="U29">
-        <v>0.0613</v>
+        <v>0.0641</v>
       </c>
       <c r="V29">
         <v>0.206</v>
       </c>
       <c r="W29">
-        <v>0.04867220000000001</v>
+        <v>0.05089540000000001</v>
       </c>
       <c r="X29" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y29">
-        <v>3.529336208297692</v>
+        <v>3.254626899015773</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -4342,22 +4342,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.08416960817713985</v>
+        <v>0.08413980153730953</v>
       </c>
       <c r="C30">
-        <v>57.7345642569467</v>
+        <v>56.93015928817608</v>
       </c>
       <c r="D30">
-        <v>74.9025642569467</v>
+        <v>74.92415928817609</v>
       </c>
       <c r="E30">
-        <v>2.527999999999999</v>
+        <v>3.353999999999999</v>
       </c>
       <c r="F30">
-        <v>23.128</v>
+        <v>23.954</v>
       </c>
       <c r="G30">
         <v>5.96</v>
@@ -4378,28 +4378,28 @@
         <v>4.824999999999999</v>
       </c>
       <c r="M30">
-        <v>1.4825048</v>
+        <v>1.5354514</v>
       </c>
       <c r="N30">
-        <v>3.342495199999999</v>
+        <v>3.289548599999999</v>
       </c>
       <c r="O30">
-        <v>0.6885540111999999</v>
+        <v>0.6776470115999998</v>
       </c>
       <c r="P30">
-        <v>2.653941188799999</v>
+        <v>2.611901588399999</v>
       </c>
       <c r="Q30">
-        <v>11.9539411888</v>
+        <v>11.9119015884</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.09710957802380536</v>
+        <v>0.09771850075677399</v>
       </c>
       <c r="T30">
-        <v>1.184978707247237</v>
+        <v>1.199041587916259</v>
       </c>
       <c r="U30">
         <v>0.0641</v>
@@ -4416,7 +4416,7 @@
         </is>
       </c>
       <c r="Y30">
-        <v>3.254626899015773</v>
+        <v>3.142398385256608</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -4424,22 +4424,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.08413980153730953</v>
+        <v>0.08410999489747921</v>
       </c>
       <c r="C31">
-        <v>56.93015928817609</v>
+        <v>56.12576677505015</v>
       </c>
       <c r="D31">
-        <v>74.92415928817609</v>
+        <v>74.94576677505016</v>
       </c>
       <c r="E31">
-        <v>3.353999999999996</v>
+        <v>4.179999999999996</v>
       </c>
       <c r="F31">
-        <v>23.954</v>
+        <v>24.78</v>
       </c>
       <c r="G31">
         <v>5.96</v>
@@ -4460,28 +4460,28 @@
         <v>4.824999999999999</v>
       </c>
       <c r="M31">
-        <v>1.5354514</v>
+        <v>1.588398</v>
       </c>
       <c r="N31">
-        <v>3.289548599999999</v>
+        <v>3.236602</v>
       </c>
       <c r="O31">
-        <v>0.6776470116</v>
+        <v>0.666740012</v>
       </c>
       <c r="P31">
-        <v>2.611901588399999</v>
+        <v>2.569861988</v>
       </c>
       <c r="Q31">
-        <v>11.9119015884</v>
+        <v>11.869861988</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.09771850075677399</v>
+        <v>0.09834482128211317</v>
       </c>
       <c r="T31">
-        <v>1.199041587916259</v>
+        <v>1.213506265175824</v>
       </c>
       <c r="U31">
         <v>0.0641</v>
@@ -4498,7 +4498,7 @@
         </is>
       </c>
       <c r="Y31">
-        <v>3.142398385256609</v>
+        <v>3.037651772414722</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -4506,22 +4506,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.08410999489747921</v>
+        <v>0.08600008025764891</v>
       </c>
       <c r="C32">
-        <v>56.12576677505015</v>
+        <v>53.95382108410531</v>
       </c>
       <c r="D32">
-        <v>74.94576677505016</v>
+        <v>73.59982108410532</v>
       </c>
       <c r="E32">
-        <v>4.179999999999996</v>
+        <v>5.005999999999997</v>
       </c>
       <c r="F32">
-        <v>24.78</v>
+        <v>25.606</v>
       </c>
       <c r="G32">
         <v>5.96</v>
@@ -4542,45 +4542,45 @@
         <v>4.824999999999999</v>
       </c>
       <c r="M32">
-        <v>1.588398</v>
+        <v>1.8410714</v>
       </c>
       <c r="N32">
-        <v>3.236602</v>
+        <v>2.9839286</v>
       </c>
       <c r="O32">
-        <v>0.666740012</v>
+        <v>0.6146892916</v>
       </c>
       <c r="P32">
-        <v>2.569861988</v>
+        <v>2.3692393084</v>
       </c>
       <c r="Q32">
-        <v>11.869861988</v>
+        <v>11.6692393084</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.09834482128211317</v>
+        <v>0.09898929602557811</v>
       </c>
       <c r="T32">
-        <v>1.213506265175824</v>
+        <v>1.228390208442913</v>
       </c>
       <c r="U32">
-        <v>0.0641</v>
+        <v>0.07190000000000001</v>
       </c>
       <c r="V32">
         <v>0.206</v>
       </c>
       <c r="W32">
-        <v>0.05089540000000001</v>
+        <v>0.05708860000000001</v>
       </c>
       <c r="X32" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y32">
-        <v>3.037651772414722</v>
+        <v>2.620756587713002</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -4588,22 +4588,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.08600008025764891</v>
+        <v>0.08603220561781857</v>
       </c>
       <c r="C33">
-        <v>53.95382108410531</v>
+        <v>53.10536204199748</v>
       </c>
       <c r="D33">
-        <v>73.59982108410532</v>
+        <v>73.57736204199749</v>
       </c>
       <c r="E33">
-        <v>5.005999999999997</v>
+        <v>5.831999999999997</v>
       </c>
       <c r="F33">
-        <v>25.606</v>
+        <v>26.432</v>
       </c>
       <c r="G33">
         <v>5.96</v>
@@ -4624,28 +4624,28 @@
         <v>4.824999999999999</v>
       </c>
       <c r="M33">
-        <v>1.8410714</v>
+        <v>1.9004608</v>
       </c>
       <c r="N33">
-        <v>2.9839286</v>
+        <v>2.924539199999999</v>
       </c>
       <c r="O33">
-        <v>0.6146892916</v>
+        <v>0.6024550751999999</v>
       </c>
       <c r="P33">
-        <v>2.3692393084</v>
+        <v>2.322084124799999</v>
       </c>
       <c r="Q33">
-        <v>11.6692393084</v>
+        <v>11.6220841248</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.09898929602557811</v>
+        <v>0.09965272590855673</v>
       </c>
       <c r="T33">
-        <v>1.228390208442913</v>
+        <v>1.243711914747269</v>
       </c>
       <c r="U33">
         <v>0.07190000000000001</v>
@@ -4662,7 +4662,7 @@
         </is>
       </c>
       <c r="Y33">
-        <v>2.620756587713002</v>
+        <v>2.538857944346971</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4670,22 +4670,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.08603220561781857</v>
+        <v>0.08708620897798824</v>
       </c>
       <c r="C34">
-        <v>53.10536204199748</v>
+        <v>51.55002837285129</v>
       </c>
       <c r="D34">
-        <v>73.57736204199749</v>
+        <v>72.84802837285129</v>
       </c>
       <c r="E34">
-        <v>5.831999999999997</v>
+        <v>6.657999999999998</v>
       </c>
       <c r="F34">
-        <v>26.432</v>
+        <v>27.258</v>
       </c>
       <c r="G34">
         <v>5.96</v>
@@ -4706,45 +4706,45 @@
         <v>4.824999999999999</v>
       </c>
       <c r="M34">
-        <v>1.9004608</v>
+        <v>2.0661564</v>
       </c>
       <c r="N34">
-        <v>2.924539199999999</v>
+        <v>2.758843599999999</v>
       </c>
       <c r="O34">
-        <v>0.6024550751999999</v>
+        <v>0.5683217815999999</v>
       </c>
       <c r="P34">
-        <v>2.322084124799999</v>
+        <v>2.190521818399999</v>
       </c>
       <c r="Q34">
-        <v>11.6220841248</v>
+        <v>11.4905218184</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.09965272590855673</v>
+        <v>0.1003359596686392</v>
       </c>
       <c r="T34">
-        <v>1.243711914747269</v>
+        <v>1.259490985418919</v>
       </c>
       <c r="U34">
-        <v>0.07190000000000001</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V34">
         <v>0.206</v>
       </c>
       <c r="W34">
-        <v>0.05708860000000001</v>
+        <v>0.06018520000000001</v>
       </c>
       <c r="X34" t="inlineStr">
         <is>
-          <t>B1/B+</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y34">
-        <v>2.538857944346971</v>
+        <v>2.335254001100787</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4752,22 +4752,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.08708620897798824</v>
+        <v>0.08714930033815793</v>
       </c>
       <c r="C35">
-        <v>51.55002837285129</v>
+        <v>50.68082972679464</v>
       </c>
       <c r="D35">
-        <v>72.84802837285129</v>
+        <v>72.80482972679465</v>
       </c>
       <c r="E35">
-        <v>6.657999999999998</v>
+        <v>7.483999999999998</v>
       </c>
       <c r="F35">
-        <v>27.258</v>
+        <v>28.084</v>
       </c>
       <c r="G35">
         <v>5.96</v>
@@ -4788,28 +4788,28 @@
         <v>4.824999999999999</v>
       </c>
       <c r="M35">
-        <v>2.0661564</v>
+        <v>2.1287672</v>
       </c>
       <c r="N35">
-        <v>2.758843599999999</v>
+        <v>2.696232799999999</v>
       </c>
       <c r="O35">
-        <v>0.5683217815999999</v>
+        <v>0.5554239567999999</v>
       </c>
       <c r="P35">
-        <v>2.190521818399999</v>
+        <v>2.140808843199999</v>
       </c>
       <c r="Q35">
-        <v>11.4905218184</v>
+        <v>11.4408088432</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.1003359596686392</v>
+        <v>0.1010398974820575</v>
       </c>
       <c r="T35">
-        <v>1.259490985418919</v>
+        <v>1.275748209747286</v>
       </c>
       <c r="U35">
         <v>0.07580000000000001</v>
@@ -4826,7 +4826,7 @@
         </is>
       </c>
       <c r="Y35">
-        <v>2.335254001100787</v>
+        <v>2.266570059891941</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4834,22 +4834,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.08714930033815793</v>
+        <v>0.08721239169832762</v>
       </c>
       <c r="C36">
-        <v>50.68082972679464</v>
+        <v>49.81168228369062</v>
       </c>
       <c r="D36">
-        <v>72.80482972679465</v>
+        <v>72.76168228369062</v>
       </c>
       <c r="E36">
-        <v>7.483999999999998</v>
+        <v>8.309999999999999</v>
       </c>
       <c r="F36">
-        <v>28.084</v>
+        <v>28.91</v>
       </c>
       <c r="G36">
         <v>5.96</v>
@@ -4870,28 +4870,28 @@
         <v>4.824999999999999</v>
       </c>
       <c r="M36">
-        <v>2.1287672</v>
+        <v>2.191378</v>
       </c>
       <c r="N36">
-        <v>2.696232799999999</v>
+        <v>2.633621999999999</v>
       </c>
       <c r="O36">
-        <v>0.5554239567999999</v>
+        <v>0.5425261319999999</v>
       </c>
       <c r="P36">
-        <v>2.140808843199999</v>
+        <v>2.091095867999999</v>
       </c>
       <c r="Q36">
-        <v>11.4408088432</v>
+        <v>11.391095868</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.1010398974820575</v>
+        <v>0.101765494920504</v>
       </c>
       <c r="T36">
-        <v>1.275748209747286</v>
+        <v>1.29250565636268</v>
       </c>
       <c r="U36">
         <v>0.07580000000000001</v>
@@ -4908,7 +4908,7 @@
         </is>
       </c>
       <c r="Y36">
-        <v>2.266570059891941</v>
+        <v>2.201810915323599</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4916,22 +4916,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.08721239169832762</v>
+        <v>0.08727548305849728</v>
       </c>
       <c r="C37">
-        <v>49.81168228369062</v>
+        <v>48.94258595255755</v>
       </c>
       <c r="D37">
-        <v>72.76168228369062</v>
+        <v>72.71858595255756</v>
       </c>
       <c r="E37">
-        <v>8.309999999999999</v>
+        <v>9.135999999999999</v>
       </c>
       <c r="F37">
-        <v>28.91</v>
+        <v>29.736</v>
       </c>
       <c r="G37">
         <v>5.96</v>
@@ -4952,28 +4952,28 @@
         <v>4.824999999999999</v>
       </c>
       <c r="M37">
-        <v>2.191378</v>
+        <v>2.2539888</v>
       </c>
       <c r="N37">
-        <v>2.633621999999999</v>
+        <v>2.571011199999999</v>
       </c>
       <c r="O37">
-        <v>0.5425261319999999</v>
+        <v>0.5296283071999999</v>
       </c>
       <c r="P37">
-        <v>2.091095867999999</v>
+        <v>2.041382892799999</v>
       </c>
       <c r="Q37">
-        <v>11.391095868</v>
+        <v>11.3413828928</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.101765494920504</v>
+        <v>0.102513767278902</v>
       </c>
       <c r="T37">
-        <v>1.29250565636268</v>
+        <v>1.309786773184804</v>
       </c>
       <c r="U37">
         <v>0.07580000000000001</v>
@@ -4990,7 +4990,7 @@
         </is>
       </c>
       <c r="Y37">
-        <v>2.201810915323599</v>
+        <v>2.140649501009055</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4998,22 +4998,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.08727548305849729</v>
+        <v>0.08733857441866698</v>
       </c>
       <c r="C38">
-        <v>48.94258595255753</v>
+        <v>48.07354064262917</v>
       </c>
       <c r="D38">
-        <v>72.71858595255753</v>
+        <v>72.67554064262917</v>
       </c>
       <c r="E38">
-        <v>9.135999999999996</v>
+        <v>9.961999999999996</v>
       </c>
       <c r="F38">
-        <v>29.736</v>
+        <v>30.562</v>
       </c>
       <c r="G38">
         <v>5.96</v>
@@ -5034,28 +5034,28 @@
         <v>4.824999999999999</v>
       </c>
       <c r="M38">
-        <v>2.2539888</v>
+        <v>2.3165996</v>
       </c>
       <c r="N38">
-        <v>2.571011199999999</v>
+        <v>2.508400399999999</v>
       </c>
       <c r="O38">
-        <v>0.5296283071999999</v>
+        <v>0.5167304823999999</v>
       </c>
       <c r="P38">
-        <v>2.041382892799999</v>
+        <v>1.991669917599999</v>
       </c>
       <c r="Q38">
-        <v>11.3413828928</v>
+        <v>11.2916699176</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.102513767278902</v>
+        <v>0.1032857943153444</v>
       </c>
       <c r="T38">
-        <v>1.309786773184804</v>
+        <v>1.327616496890171</v>
       </c>
       <c r="U38">
         <v>0.07580000000000001</v>
@@ -5072,7 +5072,7 @@
         </is>
       </c>
       <c r="Y38">
-        <v>2.140649501009055</v>
+        <v>2.082794109089892</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -5080,22 +5080,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.08733857441866698</v>
+        <v>0.08740166577883665</v>
       </c>
       <c r="C39">
-        <v>48.07354064262917</v>
+        <v>47.2045462633541</v>
       </c>
       <c r="D39">
-        <v>72.67554064262917</v>
+        <v>72.6325462633541</v>
       </c>
       <c r="E39">
-        <v>9.961999999999996</v>
+        <v>10.788</v>
       </c>
       <c r="F39">
-        <v>30.562</v>
+        <v>31.388</v>
       </c>
       <c r="G39">
         <v>5.96</v>
@@ -5116,28 +5116,28 @@
         <v>4.824999999999999</v>
       </c>
       <c r="M39">
-        <v>2.3165996</v>
+        <v>2.3792104</v>
       </c>
       <c r="N39">
-        <v>2.508400399999999</v>
+        <v>2.445789599999999</v>
       </c>
       <c r="O39">
-        <v>0.5167304823999999</v>
+        <v>0.5038326576</v>
       </c>
       <c r="P39">
-        <v>1.991669917599999</v>
+        <v>1.9419569424</v>
       </c>
       <c r="Q39">
-        <v>11.2916699176</v>
+        <v>11.2419569424</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.1032857943153444</v>
+        <v>0.1040827254497365</v>
       </c>
       <c r="T39">
-        <v>1.327616496890171</v>
+        <v>1.34602137297313</v>
       </c>
       <c r="U39">
         <v>0.07580000000000001</v>
@@ -5154,7 +5154,7 @@
         </is>
       </c>
       <c r="Y39">
-        <v>2.082794109089892</v>
+        <v>2.027983737798053</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -5162,22 +5162,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.08740166577883665</v>
+        <v>0.09186192913900633</v>
       </c>
       <c r="C40">
-        <v>47.2045462633541</v>
+        <v>43.46278877721602</v>
       </c>
       <c r="D40">
-        <v>72.6325462633541</v>
+        <v>69.71678877721602</v>
       </c>
       <c r="E40">
-        <v>10.788</v>
+        <v>11.614</v>
       </c>
       <c r="F40">
-        <v>31.388</v>
+        <v>32.214</v>
       </c>
       <c r="G40">
         <v>5.96</v>
@@ -5198,45 +5198,45 @@
         <v>4.824999999999999</v>
       </c>
       <c r="M40">
-        <v>2.3792104</v>
+        <v>2.89926</v>
       </c>
       <c r="N40">
-        <v>2.445789599999999</v>
+        <v>1.925739999999999</v>
       </c>
       <c r="O40">
-        <v>0.5038326576</v>
+        <v>0.3967024399999999</v>
       </c>
       <c r="P40">
-        <v>1.9419569424</v>
+        <v>1.529037559999999</v>
       </c>
       <c r="Q40">
-        <v>11.2419569424</v>
+        <v>10.82903756</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.1040827254497365</v>
+        <v>0.1049057854737809</v>
       </c>
       <c r="T40">
-        <v>1.34602137297313</v>
+        <v>1.365029687616186</v>
       </c>
       <c r="U40">
-        <v>0.07580000000000001</v>
+        <v>0.09</v>
       </c>
       <c r="V40">
         <v>0.206</v>
       </c>
       <c r="W40">
-        <v>0.06018520000000001</v>
+        <v>0.07146</v>
       </c>
       <c r="X40" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y40">
-        <v>2.027983737798053</v>
+        <v>1.664217765912681</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -5244,22 +5244,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.09186192913900633</v>
+        <v>0.09203776849917601</v>
       </c>
       <c r="C41">
-        <v>43.46278877721602</v>
+        <v>42.52662817066635</v>
       </c>
       <c r="D41">
-        <v>69.71678877721602</v>
+        <v>69.60662817066635</v>
       </c>
       <c r="E41">
-        <v>11.614</v>
+        <v>12.44</v>
       </c>
       <c r="F41">
-        <v>32.214</v>
+        <v>33.04</v>
       </c>
       <c r="G41">
         <v>5.96</v>
@@ -5280,28 +5280,28 @@
         <v>4.824999999999999</v>
       </c>
       <c r="M41">
-        <v>2.89926</v>
+        <v>2.9736</v>
       </c>
       <c r="N41">
-        <v>1.925739999999999</v>
+        <v>1.851399999999999</v>
       </c>
       <c r="O41">
-        <v>0.3967024399999999</v>
+        <v>0.3813883999999999</v>
       </c>
       <c r="P41">
-        <v>1.529037559999999</v>
+        <v>1.4700116</v>
       </c>
       <c r="Q41">
-        <v>10.82903756</v>
+        <v>10.7700116</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.1049057854737809</v>
+        <v>0.10575628083196</v>
       </c>
       <c r="T41">
-        <v>1.365029687616186</v>
+        <v>1.384671612747345</v>
       </c>
       <c r="U41">
         <v>0.09</v>
@@ -5318,7 +5318,7 @@
         </is>
       </c>
       <c r="Y41">
-        <v>1.664217765912681</v>
+        <v>1.622612321764864</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -5326,22 +5326,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.09203776849917601</v>
+        <v>0.09221360785934568</v>
       </c>
       <c r="C42">
-        <v>42.52662817066635</v>
+        <v>41.59081514794622</v>
       </c>
       <c r="D42">
-        <v>69.60662817066635</v>
+        <v>69.49681514794622</v>
       </c>
       <c r="E42">
-        <v>12.44</v>
+        <v>13.266</v>
       </c>
       <c r="F42">
-        <v>33.04</v>
+        <v>33.866</v>
       </c>
       <c r="G42">
         <v>5.96</v>
@@ -5362,28 +5362,28 @@
         <v>4.824999999999999</v>
       </c>
       <c r="M42">
-        <v>2.9736</v>
+        <v>3.04794</v>
       </c>
       <c r="N42">
-        <v>1.851399999999999</v>
+        <v>1.77706</v>
       </c>
       <c r="O42">
-        <v>0.3813883999999999</v>
+        <v>0.3660743599999999</v>
       </c>
       <c r="P42">
-        <v>1.4700116</v>
+        <v>1.41098564</v>
       </c>
       <c r="Q42">
-        <v>10.7700116</v>
+        <v>10.71098564</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.10575628083196</v>
+        <v>0.1066356065412639</v>
       </c>
       <c r="T42">
-        <v>1.384671612747345</v>
+        <v>1.40497936584905</v>
       </c>
       <c r="U42">
         <v>0.09</v>
@@ -5400,7 +5400,7 @@
         </is>
       </c>
       <c r="Y42">
-        <v>1.622612321764864</v>
+        <v>1.583036411477916</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -5408,22 +5408,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.09221360785934568</v>
+        <v>0.09238944721951538</v>
       </c>
       <c r="C43">
-        <v>41.59081514794622</v>
+        <v>40.65534806657799</v>
       </c>
       <c r="D43">
-        <v>69.49681514794622</v>
+        <v>69.387348066578</v>
       </c>
       <c r="E43">
-        <v>13.266</v>
+        <v>14.092</v>
       </c>
       <c r="F43">
-        <v>33.866</v>
+        <v>34.692</v>
       </c>
       <c r="G43">
         <v>5.96</v>
@@ -5444,28 +5444,28 @@
         <v>4.824999999999999</v>
       </c>
       <c r="M43">
-        <v>3.04794</v>
+        <v>3.12228</v>
       </c>
       <c r="N43">
-        <v>1.77706</v>
+        <v>1.702719999999999</v>
       </c>
       <c r="O43">
-        <v>0.3660743599999999</v>
+        <v>0.3507603199999999</v>
       </c>
       <c r="P43">
-        <v>1.41098564</v>
+        <v>1.351959679999999</v>
       </c>
       <c r="Q43">
-        <v>10.71098564</v>
+        <v>10.65195968</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.1066356065412639</v>
+        <v>0.1075452538267506</v>
       </c>
       <c r="T43">
-        <v>1.40497936584905</v>
+        <v>1.425987386299091</v>
       </c>
       <c r="U43">
         <v>0.09</v>
@@ -5482,7 +5482,7 @@
         </is>
       </c>
       <c r="Y43">
-        <v>1.583036411477916</v>
+        <v>1.545345068347489</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -5490,22 +5490,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.09238944721951536</v>
+        <v>0.09256528657968505</v>
       </c>
       <c r="C44">
-        <v>40.65534806657801</v>
+        <v>39.72022529441637</v>
       </c>
       <c r="D44">
-        <v>69.38734806657801</v>
+        <v>69.27822529441637</v>
       </c>
       <c r="E44">
-        <v>14.09199999999999</v>
+        <v>14.91799999999999</v>
       </c>
       <c r="F44">
-        <v>34.69199999999999</v>
+        <v>35.51799999999999</v>
       </c>
       <c r="G44">
         <v>5.96</v>
@@ -5526,28 +5526,28 @@
         <v>4.824999999999999</v>
       </c>
       <c r="M44">
-        <v>3.122279999999999</v>
+        <v>3.196619999999999</v>
       </c>
       <c r="N44">
-        <v>1.70272</v>
+        <v>1.62838</v>
       </c>
       <c r="O44">
-        <v>0.3507603200000001</v>
+        <v>0.33544628</v>
       </c>
       <c r="P44">
-        <v>1.35195968</v>
+        <v>1.29293372</v>
       </c>
       <c r="Q44">
-        <v>10.65195968</v>
+        <v>10.59293372</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.1075452538267506</v>
+        <v>0.108486818560851</v>
       </c>
       <c r="T44">
-        <v>1.425987386299091</v>
+        <v>1.447732530273694</v>
       </c>
       <c r="U44">
         <v>0.09</v>
@@ -5564,7 +5564,7 @@
         </is>
       </c>
       <c r="Y44">
-        <v>1.54534506834749</v>
+        <v>1.50940681094406</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -5572,22 +5572,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.09256528657968505</v>
+        <v>0.1141973074255685</v>
       </c>
       <c r="C45">
-        <v>39.72022529441637</v>
+        <v>27.66367735608097</v>
       </c>
       <c r="D45">
-        <v>69.27822529441637</v>
+        <v>58.04767735608098</v>
       </c>
       <c r="E45">
-        <v>14.91799999999999</v>
+        <v>15.744</v>
       </c>
       <c r="F45">
-        <v>35.51799999999999</v>
+        <v>36.344</v>
       </c>
       <c r="G45">
         <v>5.96</v>
@@ -5608,45 +5608,45 @@
         <v>4.824999999999999</v>
       </c>
       <c r="M45">
-        <v>3.196619999999999</v>
+        <v>5.335299200000001</v>
       </c>
       <c r="N45">
-        <v>1.62838</v>
+        <v>-0.5102992000000013</v>
       </c>
       <c r="O45">
-        <v>0.33544628</v>
+        <v>-0.1051216352000003</v>
       </c>
       <c r="P45">
-        <v>1.29293372</v>
+        <v>-0.405177564800001</v>
       </c>
       <c r="Q45">
-        <v>10.59293372</v>
+        <v>8.8948224352</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.108486818560851</v>
+        <v>0.1100689292924585</v>
       </c>
       <c r="T45">
-        <v>1.447732530273694</v>
+        <v>1.48427088435239</v>
       </c>
       <c r="U45">
-        <v>0.09</v>
+        <v>0.1468</v>
       </c>
       <c r="V45">
-        <v>0.206</v>
+        <v>0.1862969559420397</v>
       </c>
       <c r="W45">
-        <v>0.07146</v>
+        <v>0.1194516068677086</v>
       </c>
       <c r="X45" t="inlineStr">
         <is>
-          <t>B3/B-</t>
+          <t>Ca2/CC</t>
         </is>
       </c>
       <c r="Y45">
-        <v>1.50940681094406</v>
+        <v>0.9043541550584452</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5654,22 +5654,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.1141973074255685</v>
+        <v>0.1152073074255685</v>
       </c>
       <c r="C46">
-        <v>27.66367735608097</v>
+        <v>26.40162503890561</v>
       </c>
       <c r="D46">
-        <v>58.04767735608098</v>
+        <v>57.61162503890561</v>
       </c>
       <c r="E46">
-        <v>15.744</v>
+        <v>16.57</v>
       </c>
       <c r="F46">
-        <v>36.344</v>
+        <v>37.17</v>
       </c>
       <c r="G46">
         <v>5.96</v>
@@ -5690,37 +5690,37 @@
         <v>4.824999999999999</v>
       </c>
       <c r="M46">
-        <v>5.335299200000001</v>
+        <v>5.456556000000001</v>
       </c>
       <c r="N46">
-        <v>-0.5102992000000013</v>
+        <v>-0.6315560000000016</v>
       </c>
       <c r="O46">
-        <v>-0.1051216352000003</v>
+        <v>-0.1301005360000003</v>
       </c>
       <c r="P46">
-        <v>-0.405177564800001</v>
+        <v>-0.5014554640000013</v>
       </c>
       <c r="Q46">
-        <v>8.8948224352</v>
+        <v>8.798544536</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.1100689292924585</v>
+        <v>0.1112374552795941</v>
       </c>
       <c r="T46">
-        <v>1.48427088435239</v>
+        <v>1.511257627704252</v>
       </c>
       <c r="U46">
         <v>0.1468</v>
       </c>
       <c r="V46">
-        <v>0.1862969559420397</v>
+        <v>0.1821570235877722</v>
       </c>
       <c r="W46">
-        <v>0.1194516068677086</v>
+        <v>0.1200593489373151</v>
       </c>
       <c r="X46" t="inlineStr">
         <is>
@@ -5728,7 +5728,7 @@
         </is>
       </c>
       <c r="Y46">
-        <v>0.9043541550584452</v>
+        <v>0.8842573960571464</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5736,22 +5736,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.1152073074255685</v>
+        <v>0.1162173074255685</v>
       </c>
       <c r="C47">
-        <v>26.40162503890561</v>
+        <v>25.14607509852382</v>
       </c>
       <c r="D47">
-        <v>57.61162503890561</v>
+        <v>57.18207509852382</v>
       </c>
       <c r="E47">
-        <v>16.57</v>
+        <v>17.396</v>
       </c>
       <c r="F47">
-        <v>37.17</v>
+        <v>37.996</v>
       </c>
       <c r="G47">
         <v>5.96</v>
@@ -5772,37 +5772,37 @@
         <v>4.824999999999999</v>
       </c>
       <c r="M47">
-        <v>5.456556000000001</v>
+        <v>5.577812800000001</v>
       </c>
       <c r="N47">
-        <v>-0.6315560000000016</v>
+        <v>-0.7528128000000018</v>
       </c>
       <c r="O47">
-        <v>-0.1301005360000003</v>
+        <v>-0.1550794368000004</v>
       </c>
       <c r="P47">
-        <v>-0.5014554640000013</v>
+        <v>-0.5977333632000015</v>
       </c>
       <c r="Q47">
-        <v>8.798544536</v>
+        <v>8.702266636799999</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.1112374552795941</v>
+        <v>0.112449260006994</v>
       </c>
       <c r="T47">
-        <v>1.511257627704252</v>
+        <v>1.539243880069145</v>
       </c>
       <c r="U47">
         <v>0.1468</v>
       </c>
       <c r="V47">
-        <v>0.1821570235877722</v>
+        <v>0.1781970882923858</v>
       </c>
       <c r="W47">
-        <v>0.1200593489373151</v>
+        <v>0.1206406674386778</v>
       </c>
       <c r="X47" t="inlineStr">
         <is>
@@ -5810,7 +5810,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>0.8842573960571464</v>
+        <v>0.8650344091863389</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5818,22 +5818,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.1162173074255685</v>
+        <v>0.1172273074255686</v>
       </c>
       <c r="C48">
-        <v>25.14607509852382</v>
+        <v>23.89688316696412</v>
       </c>
       <c r="D48">
-        <v>57.18207509852382</v>
+        <v>56.75888316696413</v>
       </c>
       <c r="E48">
-        <v>17.396</v>
+        <v>18.222</v>
       </c>
       <c r="F48">
-        <v>37.996</v>
+        <v>38.822</v>
       </c>
       <c r="G48">
         <v>5.96</v>
@@ -5854,37 +5854,37 @@
         <v>4.824999999999999</v>
       </c>
       <c r="M48">
-        <v>5.577812800000001</v>
+        <v>5.699069600000001</v>
       </c>
       <c r="N48">
-        <v>-0.7528128000000018</v>
+        <v>-0.8740696000000012</v>
       </c>
       <c r="O48">
-        <v>-0.1550794368000004</v>
+        <v>-0.1800583376000003</v>
       </c>
       <c r="P48">
-        <v>-0.5977333632000015</v>
+        <v>-0.694011262400001</v>
       </c>
       <c r="Q48">
-        <v>8.702266636799999</v>
+        <v>8.605988737600001</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.112449260006994</v>
+        <v>0.1137067932146731</v>
       </c>
       <c r="T48">
-        <v>1.539243880069145</v>
+        <v>1.568286217428941</v>
       </c>
       <c r="U48">
         <v>0.1468</v>
       </c>
       <c r="V48">
-        <v>0.1781970882923858</v>
+        <v>0.1744056608819095</v>
       </c>
       <c r="W48">
-        <v>0.1206406674386778</v>
+        <v>0.1211972489825357</v>
       </c>
       <c r="X48" t="inlineStr">
         <is>
@@ -5892,7 +5892,7 @@
         </is>
       </c>
       <c r="Y48">
-        <v>0.8650344091863389</v>
+        <v>0.8466294217568424</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5900,22 +5900,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.1172273074255686</v>
+        <v>0.1182373074255685</v>
       </c>
       <c r="C49">
-        <v>23.89688316696412</v>
+        <v>22.65390911860057</v>
       </c>
       <c r="D49">
-        <v>56.75888316696413</v>
+        <v>56.34190911860058</v>
       </c>
       <c r="E49">
-        <v>18.222</v>
+        <v>19.048</v>
       </c>
       <c r="F49">
-        <v>38.822</v>
+        <v>39.648</v>
       </c>
       <c r="G49">
         <v>5.96</v>
@@ -5936,37 +5936,37 @@
         <v>4.824999999999999</v>
       </c>
       <c r="M49">
-        <v>5.699069600000001</v>
+        <v>5.820326400000001</v>
       </c>
       <c r="N49">
-        <v>-0.8740696000000012</v>
+        <v>-0.9953264000000015</v>
       </c>
       <c r="O49">
-        <v>-0.1800583376000003</v>
+        <v>-0.2050372384000003</v>
       </c>
       <c r="P49">
-        <v>-0.694011262400001</v>
+        <v>-0.7902891616000012</v>
       </c>
       <c r="Q49">
-        <v>8.605988737600001</v>
+        <v>8.5097108384</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.1137067932146731</v>
+        <v>0.1150126930841861</v>
       </c>
       <c r="T49">
-        <v>1.568286217428941</v>
+        <v>1.598445567764113</v>
       </c>
       <c r="U49">
         <v>0.1468</v>
       </c>
       <c r="V49">
-        <v>0.1744056608819095</v>
+        <v>0.1707722096135364</v>
       </c>
       <c r="W49">
-        <v>0.1211972489825357</v>
+        <v>0.1217306396287329</v>
       </c>
       <c r="X49" t="inlineStr">
         <is>
@@ -5974,7 +5974,7 @@
         </is>
       </c>
       <c r="Y49">
-        <v>0.8466294217568424</v>
+        <v>0.8289913088035747</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5982,22 +5982,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.1182373074255685</v>
+        <v>0.1192473074255685</v>
       </c>
       <c r="C50">
-        <v>22.65390911860058</v>
+        <v>21.417016915459</v>
       </c>
       <c r="D50">
-        <v>56.34190911860058</v>
+        <v>55.931016915459</v>
       </c>
       <c r="E50">
-        <v>19.04799999999999</v>
+        <v>19.874</v>
       </c>
       <c r="F50">
-        <v>39.648</v>
+        <v>40.474</v>
       </c>
       <c r="G50">
         <v>5.96</v>
@@ -6018,37 +6018,37 @@
         <v>4.824999999999999</v>
       </c>
       <c r="M50">
-        <v>5.8203264</v>
+        <v>5.9415832</v>
       </c>
       <c r="N50">
-        <v>-0.9953264000000006</v>
+        <v>-1.116583200000001</v>
       </c>
       <c r="O50">
-        <v>-0.2050372384000002</v>
+        <v>-0.2300161392000002</v>
       </c>
       <c r="P50">
-        <v>-0.7902891616000005</v>
+        <v>-0.8865670608000007</v>
       </c>
       <c r="Q50">
-        <v>8.5097108384</v>
+        <v>8.4134329392</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.1150126930841861</v>
+        <v>0.1163698047132878</v>
       </c>
       <c r="T50">
-        <v>1.598445567764113</v>
+        <v>1.629787637720272</v>
       </c>
       <c r="U50">
         <v>0.1468</v>
       </c>
       <c r="V50">
-        <v>0.1707722096135364</v>
+        <v>0.1672870624785663</v>
       </c>
       <c r="W50">
-        <v>0.1217306396287329</v>
+        <v>0.1222422592281465</v>
       </c>
       <c r="X50" t="inlineStr">
         <is>
@@ -6056,7 +6056,7 @@
         </is>
       </c>
       <c r="Y50">
-        <v>0.8289913088035749</v>
+        <v>0.8120731188279917</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -6064,22 +6064,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.1192473074255685</v>
+        <v>0.1481215208677252</v>
       </c>
       <c r="C51">
-        <v>21.417016915459</v>
+        <v>10.94173928954836</v>
       </c>
       <c r="D51">
-        <v>55.931016915459</v>
+        <v>46.28173928954836</v>
       </c>
       <c r="E51">
-        <v>19.874</v>
+        <v>20.7</v>
       </c>
       <c r="F51">
-        <v>40.474</v>
+        <v>41.3</v>
       </c>
       <c r="G51">
         <v>5.96</v>
@@ -6100,45 +6100,45 @@
         <v>4.824999999999999</v>
       </c>
       <c r="M51">
-        <v>5.9415832</v>
+        <v>8.29304</v>
       </c>
       <c r="N51">
-        <v>-1.116583200000001</v>
+        <v>-3.46804</v>
       </c>
       <c r="O51">
-        <v>-0.2300161392000002</v>
+        <v>-0.7144162400000001</v>
       </c>
       <c r="P51">
-        <v>-0.8865670608000007</v>
+        <v>-2.75362376</v>
       </c>
       <c r="Q51">
-        <v>8.4134329392</v>
+        <v>6.546376240000001</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.1163698047132878</v>
+        <v>0.1195096276918668</v>
       </c>
       <c r="T51">
-        <v>1.629787637720272</v>
+        <v>1.702300870481912</v>
       </c>
       <c r="U51">
-        <v>0.1468</v>
+        <v>0.2008</v>
       </c>
       <c r="V51">
-        <v>0.1672870624785663</v>
+        <v>0.1198535157192055</v>
       </c>
       <c r="W51">
-        <v>0.1222422592281465</v>
+        <v>0.1767334140435835</v>
       </c>
       <c r="X51" t="inlineStr">
         <is>
-          <t>Ca2/CC</t>
+          <t>C2/C</t>
         </is>
       </c>
       <c r="Y51">
-        <v>0.8120731188279917</v>
+        <v>0.5818131831029393</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -6146,22 +6146,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.1481215208677252</v>
+        <v>0.1496715208677252</v>
       </c>
       <c r="C52">
-        <v>10.94173928954836</v>
+        <v>9.691051524492124</v>
       </c>
       <c r="D52">
-        <v>46.28173928954836</v>
+        <v>45.85705152449212</v>
       </c>
       <c r="E52">
-        <v>20.7</v>
+        <v>21.526</v>
       </c>
       <c r="F52">
-        <v>41.3</v>
+        <v>42.126</v>
       </c>
       <c r="G52">
         <v>5.96</v>
@@ -6182,37 +6182,37 @@
         <v>4.824999999999999</v>
       </c>
       <c r="M52">
-        <v>8.29304</v>
+        <v>8.4589008</v>
       </c>
       <c r="N52">
-        <v>-3.46804</v>
+        <v>-3.633900800000001</v>
       </c>
       <c r="O52">
-        <v>-0.7144162400000001</v>
+        <v>-0.7485835648000003</v>
       </c>
       <c r="P52">
-        <v>-2.75362376</v>
+        <v>-2.8853172352</v>
       </c>
       <c r="Q52">
-        <v>6.546376240000001</v>
+        <v>6.4146827648</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.1195096276918668</v>
+        <v>0.1210139058080273</v>
       </c>
       <c r="T52">
-        <v>1.702300870481912</v>
+        <v>1.73704170457338</v>
       </c>
       <c r="U52">
         <v>0.2008</v>
       </c>
       <c r="V52">
-        <v>0.1198535157192055</v>
+        <v>0.1175034467835348</v>
       </c>
       <c r="W52">
-        <v>0.1767334140435835</v>
+        <v>0.1772053078858662</v>
       </c>
       <c r="X52" t="inlineStr">
         <is>
@@ -6220,7 +6220,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>0.5818131831029393</v>
+        <v>0.5704050814734698</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -6228,22 +6228,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.1496715208677252</v>
+        <v>0.1512215208677252</v>
       </c>
       <c r="C53">
-        <v>9.691051524492124</v>
+        <v>8.44808688060624</v>
       </c>
       <c r="D53">
-        <v>45.85705152449212</v>
+        <v>45.44008688060624</v>
       </c>
       <c r="E53">
-        <v>21.526</v>
+        <v>22.352</v>
       </c>
       <c r="F53">
-        <v>42.126</v>
+        <v>42.952</v>
       </c>
       <c r="G53">
         <v>5.96</v>
@@ -6264,37 +6264,37 @@
         <v>4.824999999999999</v>
       </c>
       <c r="M53">
-        <v>8.4589008</v>
+        <v>8.624761599999999</v>
       </c>
       <c r="N53">
-        <v>-3.633900800000001</v>
+        <v>-3.7997616</v>
       </c>
       <c r="O53">
-        <v>-0.7485835648000003</v>
+        <v>-0.7827508896000001</v>
       </c>
       <c r="P53">
-        <v>-2.8853172352</v>
+        <v>-3.0170107104</v>
       </c>
       <c r="Q53">
-        <v>6.4146827648</v>
+        <v>6.282989289600001</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.1210139058080273</v>
+        <v>0.1225808621790279</v>
       </c>
       <c r="T53">
-        <v>1.73704170457338</v>
+        <v>1.773230073418658</v>
       </c>
       <c r="U53">
         <v>0.2008</v>
       </c>
       <c r="V53">
-        <v>0.1175034467835348</v>
+        <v>0.1152437651146207</v>
       </c>
       <c r="W53">
-        <v>0.1772053078858662</v>
+        <v>0.1776590519649842</v>
       </c>
       <c r="X53" t="inlineStr">
         <is>
@@ -6302,7 +6302,7 @@
         </is>
       </c>
       <c r="Y53">
-        <v>0.5704050814734698</v>
+        <v>0.5594357529835955</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -6310,22 +6310,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.1512215208677252</v>
+        <v>0.1527715208677252</v>
       </c>
       <c r="C54">
-        <v>8.44808688060624</v>
+        <v>7.212636584021368</v>
       </c>
       <c r="D54">
-        <v>45.44008688060624</v>
+        <v>45.03063658402137</v>
       </c>
       <c r="E54">
-        <v>22.352</v>
+        <v>23.178</v>
       </c>
       <c r="F54">
-        <v>42.952</v>
+        <v>43.778</v>
       </c>
       <c r="G54">
         <v>5.96</v>
@@ -6346,37 +6346,37 @@
         <v>4.824999999999999</v>
       </c>
       <c r="M54">
-        <v>8.624761599999999</v>
+        <v>8.7906224</v>
       </c>
       <c r="N54">
-        <v>-3.7997616</v>
+        <v>-3.965622400000001</v>
       </c>
       <c r="O54">
-        <v>-0.7827508896000001</v>
+        <v>-0.8169182144000002</v>
       </c>
       <c r="P54">
-        <v>-3.0170107104</v>
+        <v>-3.148704185600001</v>
       </c>
       <c r="Q54">
-        <v>6.282989289600001</v>
+        <v>6.1512958144</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.1225808621790279</v>
+        <v>0.1242144975445391</v>
       </c>
       <c r="T54">
-        <v>1.773230073418658</v>
+        <v>1.810958372853098</v>
       </c>
       <c r="U54">
         <v>0.2008</v>
       </c>
       <c r="V54">
-        <v>0.1152437651146207</v>
+        <v>0.1130693544520807</v>
       </c>
       <c r="W54">
-        <v>0.1776590519649842</v>
+        <v>0.1780956736260222</v>
       </c>
       <c r="X54" t="inlineStr">
         <is>
@@ -6384,7 +6384,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>0.5594357529835955</v>
+        <v>0.5488803614178672</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -6392,22 +6392,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.1527715208677252</v>
+        <v>0.1543215208677252</v>
       </c>
       <c r="C55">
-        <v>7.212636584021368</v>
+        <v>5.984499318524492</v>
       </c>
       <c r="D55">
-        <v>45.03063658402137</v>
+        <v>44.62849931852449</v>
       </c>
       <c r="E55">
-        <v>23.178</v>
+        <v>24.004</v>
       </c>
       <c r="F55">
-        <v>43.778</v>
+        <v>44.604</v>
       </c>
       <c r="G55">
         <v>5.96</v>
@@ -6428,37 +6428,37 @@
         <v>4.824999999999999</v>
       </c>
       <c r="M55">
-        <v>8.7906224</v>
+        <v>8.956483200000001</v>
       </c>
       <c r="N55">
-        <v>-3.965622400000001</v>
+        <v>-4.131483200000002</v>
       </c>
       <c r="O55">
-        <v>-0.8169182144000002</v>
+        <v>-0.8510855392000004</v>
       </c>
       <c r="P55">
-        <v>-3.148704185600001</v>
+        <v>-3.280397660800001</v>
       </c>
       <c r="Q55">
-        <v>6.1512958144</v>
+        <v>6.0196023392</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.1242144975445391</v>
+        <v>0.1259191605346378</v>
       </c>
       <c r="T55">
-        <v>1.810958372853098</v>
+        <v>1.850327033132513</v>
       </c>
       <c r="U55">
         <v>0.2008</v>
       </c>
       <c r="V55">
-        <v>0.1130693544520807</v>
+        <v>0.1109754775177829</v>
       </c>
       <c r="W55">
-        <v>0.1780956736260222</v>
+        <v>0.1785161241144292</v>
       </c>
       <c r="X55" t="inlineStr">
         <is>
@@ -6466,7 +6466,7 @@
         </is>
       </c>
       <c r="Y55">
-        <v>0.5488803614178672</v>
+        <v>0.5387159102804993</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -6474,22 +6474,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.1543215208677252</v>
+        <v>0.1558715208677252</v>
       </c>
       <c r="C56">
-        <v>5.984499318524492</v>
+        <v>4.763480895510661</v>
       </c>
       <c r="D56">
-        <v>44.62849931852449</v>
+        <v>44.23348089551066</v>
       </c>
       <c r="E56">
-        <v>24.004</v>
+        <v>24.83</v>
       </c>
       <c r="F56">
-        <v>44.604</v>
+        <v>45.43</v>
       </c>
       <c r="G56">
         <v>5.96</v>
@@ -6510,37 +6510,37 @@
         <v>4.824999999999999</v>
       </c>
       <c r="M56">
-        <v>8.956483200000001</v>
+        <v>9.122344</v>
       </c>
       <c r="N56">
-        <v>-4.131483200000002</v>
+        <v>-4.297344000000001</v>
       </c>
       <c r="O56">
-        <v>-0.8510855392000004</v>
+        <v>-0.8852528640000003</v>
       </c>
       <c r="P56">
-        <v>-3.280397660800001</v>
+        <v>-3.412091136</v>
       </c>
       <c r="Q56">
-        <v>6.0196023392</v>
+        <v>5.887908864</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.1259191605346378</v>
+        <v>0.1276995863242964</v>
       </c>
       <c r="T56">
-        <v>1.850327033132513</v>
+        <v>1.891445411646569</v>
       </c>
       <c r="U56">
         <v>0.2008</v>
       </c>
       <c r="V56">
-        <v>0.1109754775177829</v>
+        <v>0.1089577415629141</v>
       </c>
       <c r="W56">
-        <v>0.1785161241144292</v>
+        <v>0.1789212854941669</v>
       </c>
       <c r="X56" t="inlineStr">
         <is>
@@ -6548,7 +6548,7 @@
         </is>
       </c>
       <c r="Y56">
-        <v>0.5387159102804993</v>
+        <v>0.5289210755481266</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -6556,22 +6556,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.1558715208677252</v>
+        <v>0.1574215208677252</v>
       </c>
       <c r="C57">
-        <v>4.763480895510661</v>
+        <v>3.54939394130902</v>
       </c>
       <c r="D57">
-        <v>44.23348089551066</v>
+        <v>43.84539394130902</v>
       </c>
       <c r="E57">
-        <v>24.83</v>
+        <v>25.656</v>
       </c>
       <c r="F57">
-        <v>45.43</v>
+        <v>46.256</v>
       </c>
       <c r="G57">
         <v>5.96</v>
@@ -6592,37 +6592,37 @@
         <v>4.824999999999999</v>
       </c>
       <c r="M57">
-        <v>9.122344</v>
+        <v>9.288204800000001</v>
       </c>
       <c r="N57">
-        <v>-4.297344000000001</v>
+        <v>-4.463204800000002</v>
       </c>
       <c r="O57">
-        <v>-0.8852528640000003</v>
+        <v>-0.9194201888000004</v>
       </c>
       <c r="P57">
-        <v>-3.412091136</v>
+        <v>-3.543784611200001</v>
       </c>
       <c r="Q57">
-        <v>5.887908864</v>
+        <v>5.756215388799999</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.1276995863242964</v>
+        <v>0.1295609405589395</v>
       </c>
       <c r="T57">
-        <v>1.891445411646569</v>
+        <v>1.934432807365809</v>
       </c>
       <c r="U57">
         <v>0.2008</v>
       </c>
       <c r="V57">
-        <v>0.1089577415629141</v>
+        <v>0.1070120676064335</v>
       </c>
       <c r="W57">
-        <v>0.1789212854941669</v>
+        <v>0.1793119768246282</v>
       </c>
       <c r="X57" t="inlineStr">
         <is>
@@ -6630,7 +6630,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>0.5289210755481266</v>
+        <v>0.5194760563419101</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -6638,22 +6638,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.1574215208677252</v>
+        <v>0.1589715208677252</v>
       </c>
       <c r="C58">
-        <v>3.54939394130902</v>
+        <v>2.342057600825342</v>
       </c>
       <c r="D58">
-        <v>43.84539394130902</v>
+        <v>43.46405760082534</v>
       </c>
       <c r="E58">
-        <v>25.656</v>
+        <v>26.482</v>
       </c>
       <c r="F58">
-        <v>46.256</v>
+        <v>47.082</v>
       </c>
       <c r="G58">
         <v>5.96</v>
@@ -6674,37 +6674,37 @@
         <v>4.824999999999999</v>
       </c>
       <c r="M58">
-        <v>9.288204800000001</v>
+        <v>9.4540656</v>
       </c>
       <c r="N58">
-        <v>-4.463204800000002</v>
+        <v>-4.629065600000001</v>
       </c>
       <c r="O58">
-        <v>-0.9194201888000004</v>
+        <v>-0.9535875136000002</v>
       </c>
       <c r="P58">
-        <v>-3.543784611200001</v>
+        <v>-3.675478086400001</v>
       </c>
       <c r="Q58">
-        <v>5.756215388799999</v>
+        <v>5.624521913600001</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.1295609405589395</v>
+        <v>0.1315088694091474</v>
       </c>
       <c r="T58">
-        <v>1.934432807365809</v>
+        <v>1.979419616839433</v>
       </c>
       <c r="U58">
         <v>0.2008</v>
       </c>
       <c r="V58">
-        <v>0.1070120676064335</v>
+        <v>0.1051346629115838</v>
       </c>
       <c r="W58">
-        <v>0.1793119768246282</v>
+        <v>0.179688959687354</v>
       </c>
       <c r="X58" t="inlineStr">
         <is>
@@ -6712,7 +6712,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>0.5194760563419101</v>
+        <v>0.5103624413183678</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6720,22 +6720,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.1589715208677252</v>
+        <v>0.1605215208677252</v>
       </c>
       <c r="C59">
-        <v>2.342057600825342</v>
+        <v>1.141297256516232</v>
       </c>
       <c r="D59">
-        <v>43.46405760082534</v>
+        <v>43.08929725651623</v>
       </c>
       <c r="E59">
-        <v>26.482</v>
+        <v>27.308</v>
       </c>
       <c r="F59">
-        <v>47.082</v>
+        <v>47.908</v>
       </c>
       <c r="G59">
         <v>5.96</v>
@@ -6756,37 +6756,37 @@
         <v>4.824999999999999</v>
       </c>
       <c r="M59">
-        <v>9.4540656</v>
+        <v>9.619926400000001</v>
       </c>
       <c r="N59">
-        <v>-4.629065600000001</v>
+        <v>-4.794926400000001</v>
       </c>
       <c r="O59">
-        <v>-0.9535875136000002</v>
+        <v>-0.9877548384000003</v>
       </c>
       <c r="P59">
-        <v>-3.675478086400001</v>
+        <v>-3.807171561600001</v>
       </c>
       <c r="Q59">
-        <v>5.624521913600001</v>
+        <v>5.4928284384</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.1315088694091474</v>
+        <v>0.1335495567760319</v>
       </c>
       <c r="T59">
-        <v>1.979419616839433</v>
+        <v>2.02654865533561</v>
       </c>
       <c r="U59">
         <v>0.2008</v>
       </c>
       <c r="V59">
-        <v>0.1051346629115838</v>
+        <v>0.1033219963096599</v>
       </c>
       <c r="W59">
-        <v>0.179688959687354</v>
+        <v>0.1800529431410203</v>
       </c>
       <c r="X59" t="inlineStr">
         <is>
@@ -6794,7 +6794,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>0.5103624413183678</v>
+        <v>0.5015630888818441</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6802,22 +6802,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.1605215208677252</v>
+        <v>0.1830702414301762</v>
       </c>
       <c r="C60">
-        <v>1.141297256516239</v>
+        <v>-4.487155905997724</v>
       </c>
       <c r="D60">
-        <v>43.08929725651623</v>
+        <v>38.28684409400227</v>
       </c>
       <c r="E60">
-        <v>27.30799999999999</v>
+        <v>28.13399999999999</v>
       </c>
       <c r="F60">
-        <v>47.90799999999999</v>
+        <v>48.73399999999999</v>
       </c>
       <c r="G60">
         <v>5.96</v>
@@ -6838,45 +6838,45 @@
         <v>4.824999999999999</v>
       </c>
       <c r="M60">
-        <v>9.619926399999999</v>
+        <v>11.4914772</v>
       </c>
       <c r="N60">
-        <v>-4.7949264</v>
+        <v>-6.666477199999999</v>
       </c>
       <c r="O60">
-        <v>-0.9877548384</v>
+        <v>-1.3732943032</v>
       </c>
       <c r="P60">
-        <v>-3.8071715616</v>
+        <v>-5.293182896799999</v>
       </c>
       <c r="Q60">
-        <v>5.492828438400001</v>
+        <v>4.006817103200001</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.1335495567760319</v>
+        <v>0.1365403278253277</v>
       </c>
       <c r="T60">
-        <v>2.026548655335609</v>
+        <v>2.095619580261611</v>
       </c>
       <c r="U60">
-        <v>0.2008</v>
+        <v>0.2358</v>
       </c>
       <c r="V60">
-        <v>0.1033219963096599</v>
+        <v>0.08649453701217803</v>
       </c>
       <c r="W60">
-        <v>0.1800529431410203</v>
+        <v>0.2154045881725284</v>
       </c>
       <c r="X60" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>D2/D</t>
         </is>
       </c>
       <c r="Y60">
-        <v>0.5015630888818443</v>
+        <v>0.4198763932630002</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6884,22 +6884,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.1830702414301762</v>
+        <v>0.1849702414301761</v>
       </c>
       <c r="C61">
-        <v>-4.487155905997724</v>
+        <v>-5.669373559407653</v>
       </c>
       <c r="D61">
-        <v>38.28684409400227</v>
+        <v>37.93062644059234</v>
       </c>
       <c r="E61">
-        <v>28.13399999999999</v>
+        <v>28.95999999999999</v>
       </c>
       <c r="F61">
-        <v>48.73399999999999</v>
+        <v>49.56</v>
       </c>
       <c r="G61">
         <v>5.96</v>
@@ -6920,37 +6920,37 @@
         <v>4.824999999999999</v>
       </c>
       <c r="M61">
-        <v>11.4914772</v>
+        <v>11.686248</v>
       </c>
       <c r="N61">
-        <v>-6.666477199999999</v>
+        <v>-6.861248</v>
       </c>
       <c r="O61">
-        <v>-1.3732943032</v>
+        <v>-1.413417088</v>
       </c>
       <c r="P61">
-        <v>-5.293182896799999</v>
+        <v>-5.447830912</v>
       </c>
       <c r="Q61">
-        <v>4.006817103200001</v>
+        <v>3.852169088000001</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.1365403278253277</v>
+        <v>0.1388088360209609</v>
       </c>
       <c r="T61">
-        <v>2.095619580261611</v>
+        <v>2.148010069768151</v>
       </c>
       <c r="U61">
         <v>0.2358</v>
       </c>
       <c r="V61">
-        <v>0.08649453701217803</v>
+        <v>0.08505296139530839</v>
       </c>
       <c r="W61">
-        <v>0.2154045881725284</v>
+        <v>0.2157445117029863</v>
       </c>
       <c r="X61" t="inlineStr">
         <is>
@@ -6958,7 +6958,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>0.4198763932630002</v>
+        <v>0.4128784533752835</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6966,22 +6966,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.1849702414301761</v>
+        <v>0.1868702414301762</v>
       </c>
       <c r="C62">
-        <v>-5.669373559407653</v>
+        <v>-6.845023875196674</v>
       </c>
       <c r="D62">
-        <v>37.93062644059234</v>
+        <v>37.58097612480332</v>
       </c>
       <c r="E62">
-        <v>28.95999999999999</v>
+        <v>29.78599999999999</v>
       </c>
       <c r="F62">
-        <v>49.56</v>
+        <v>50.386</v>
       </c>
       <c r="G62">
         <v>5.96</v>
@@ -7002,37 +7002,37 @@
         <v>4.824999999999999</v>
       </c>
       <c r="M62">
-        <v>11.686248</v>
+        <v>11.8810188</v>
       </c>
       <c r="N62">
-        <v>-6.861248</v>
+        <v>-7.0560188</v>
       </c>
       <c r="O62">
-        <v>-1.413417088</v>
+        <v>-1.4535398728</v>
       </c>
       <c r="P62">
-        <v>-5.447830912</v>
+        <v>-5.6024789272</v>
       </c>
       <c r="Q62">
-        <v>3.852169088000001</v>
+        <v>3.697521072800001</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.1388088360209609</v>
+        <v>0.1411936779702163</v>
       </c>
       <c r="T62">
-        <v>2.148010069768151</v>
+        <v>2.203087251044257</v>
       </c>
       <c r="U62">
         <v>0.2358</v>
       </c>
       <c r="V62">
-        <v>0.08505296139530839</v>
+        <v>0.08365865055276236</v>
       </c>
       <c r="W62">
-        <v>0.2157445117029863</v>
+        <v>0.2160732901996587</v>
       </c>
       <c r="X62" t="inlineStr">
         <is>
@@ -7040,7 +7040,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>0.4128784533752835</v>
+        <v>0.406109954139623</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -7048,22 +7048,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.1868702414301762</v>
+        <v>0.1887702414301761</v>
       </c>
       <c r="C63">
-        <v>-6.845023875196674</v>
+        <v>-8.01428681065876</v>
       </c>
       <c r="D63">
-        <v>37.58097612480332</v>
+        <v>37.23771318934124</v>
       </c>
       <c r="E63">
-        <v>29.78599999999999</v>
+        <v>30.61199999999999</v>
       </c>
       <c r="F63">
-        <v>50.386</v>
+        <v>51.212</v>
       </c>
       <c r="G63">
         <v>5.96</v>
@@ -7084,37 +7084,37 @@
         <v>4.824999999999999</v>
       </c>
       <c r="M63">
-        <v>11.8810188</v>
+        <v>12.0757896</v>
       </c>
       <c r="N63">
-        <v>-7.0560188</v>
+        <v>-7.250789600000001</v>
       </c>
       <c r="O63">
-        <v>-1.4535398728</v>
+        <v>-1.4936626576</v>
       </c>
       <c r="P63">
-        <v>-5.6024789272</v>
+        <v>-5.757126942400001</v>
       </c>
       <c r="Q63">
-        <v>3.697521072800001</v>
+        <v>3.5428730576</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.1411936779702163</v>
+        <v>0.143704037916801</v>
       </c>
       <c r="T63">
-        <v>2.203087251044257</v>
+        <v>2.261063231334896</v>
       </c>
       <c r="U63">
         <v>0.2358</v>
       </c>
       <c r="V63">
-        <v>0.08365865055276236</v>
+        <v>0.08230931747933071</v>
       </c>
       <c r="W63">
-        <v>0.2160732901996587</v>
+        <v>0.2163914629383738</v>
       </c>
       <c r="X63" t="inlineStr">
         <is>
@@ -7122,7 +7122,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>0.406109954139623</v>
+        <v>0.399559793588984</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -7130,22 +7130,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.1887702414301761</v>
+        <v>0.1906702414301762</v>
       </c>
       <c r="C64">
-        <v>-8.01428681065876</v>
+        <v>-9.177335807711977</v>
       </c>
       <c r="D64">
-        <v>37.23771318934124</v>
+        <v>36.90066419228802</v>
       </c>
       <c r="E64">
-        <v>30.61199999999999</v>
+        <v>31.438</v>
       </c>
       <c r="F64">
-        <v>51.212</v>
+        <v>52.038</v>
       </c>
       <c r="G64">
         <v>5.96</v>
@@ -7166,37 +7166,37 @@
         <v>4.824999999999999</v>
       </c>
       <c r="M64">
-        <v>12.0757896</v>
+        <v>12.2705604</v>
       </c>
       <c r="N64">
-        <v>-7.250789600000001</v>
+        <v>-7.4455604</v>
       </c>
       <c r="O64">
-        <v>-1.4936626576</v>
+        <v>-1.5337854424</v>
       </c>
       <c r="P64">
-        <v>-5.757126942400001</v>
+        <v>-5.9117749576</v>
       </c>
       <c r="Q64">
-        <v>3.5428730576</v>
+        <v>3.388225042400001</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.143704037916801</v>
+        <v>0.1463500929956335</v>
       </c>
       <c r="T64">
-        <v>2.261063231334896</v>
+        <v>2.322173048398001</v>
       </c>
       <c r="U64">
         <v>0.2358</v>
       </c>
       <c r="V64">
-        <v>0.08230931747933071</v>
+        <v>0.08100282037648419</v>
       </c>
       <c r="W64">
-        <v>0.2163914629383738</v>
+        <v>0.216699534955225</v>
       </c>
       <c r="X64" t="inlineStr">
         <is>
@@ -7204,7 +7204,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>0.399559793588984</v>
+        <v>0.3932175746431271</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -7212,22 +7212,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.1906702414301762</v>
+        <v>0.1925702414301761</v>
       </c>
       <c r="C65">
-        <v>-9.177335807711977</v>
+        <v>-10.33433808511591</v>
       </c>
       <c r="D65">
-        <v>36.90066419228802</v>
+        <v>36.56966191488409</v>
       </c>
       <c r="E65">
-        <v>31.438</v>
+        <v>32.264</v>
       </c>
       <c r="F65">
-        <v>52.038</v>
+        <v>52.864</v>
       </c>
       <c r="G65">
         <v>5.96</v>
@@ -7248,37 +7248,37 @@
         <v>4.824999999999999</v>
       </c>
       <c r="M65">
-        <v>12.2705604</v>
+        <v>12.4653312</v>
       </c>
       <c r="N65">
-        <v>-7.4455604</v>
+        <v>-7.6403312</v>
       </c>
       <c r="O65">
-        <v>-1.5337854424</v>
+        <v>-1.5739082272</v>
       </c>
       <c r="P65">
-        <v>-5.9117749576</v>
+        <v>-6.0664229728</v>
       </c>
       <c r="Q65">
-        <v>3.388225042400001</v>
+        <v>3.233577027200001</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.1463500929956335</v>
+        <v>0.149143151134401</v>
       </c>
       <c r="T65">
-        <v>2.322173048398001</v>
+        <v>2.386677855297946</v>
       </c>
       <c r="U65">
         <v>0.2358</v>
       </c>
       <c r="V65">
-        <v>0.08100282037648419</v>
+        <v>0.07973715130810162</v>
       </c>
       <c r="W65">
-        <v>0.216699534955225</v>
+        <v>0.2169979797215496</v>
       </c>
       <c r="X65" t="inlineStr">
         <is>
@@ -7286,7 +7286,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>0.3932175746431271</v>
+        <v>0.3870735500393282</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -7294,22 +7294,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.1925702414301761</v>
+        <v>0.1944702414301762</v>
       </c>
       <c r="C66">
-        <v>-10.33433808511591</v>
+        <v>-11.48545491510182</v>
       </c>
       <c r="D66">
-        <v>36.56966191488409</v>
+        <v>36.24454508489818</v>
       </c>
       <c r="E66">
-        <v>32.264</v>
+        <v>33.09</v>
       </c>
       <c r="F66">
-        <v>52.864</v>
+        <v>53.69</v>
       </c>
       <c r="G66">
         <v>5.96</v>
@@ -7330,37 +7330,37 @@
         <v>4.824999999999999</v>
       </c>
       <c r="M66">
-        <v>12.4653312</v>
+        <v>12.660102</v>
       </c>
       <c r="N66">
-        <v>-7.6403312</v>
+        <v>-7.835102000000001</v>
       </c>
       <c r="O66">
-        <v>-1.5739082272</v>
+        <v>-1.614031012</v>
       </c>
       <c r="P66">
-        <v>-6.0664229728</v>
+        <v>-6.221070988000001</v>
       </c>
       <c r="Q66">
-        <v>3.233577027200001</v>
+        <v>3.078929012</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.149143151134401</v>
+        <v>0.1520958125953839</v>
       </c>
       <c r="T66">
-        <v>2.386677855297946</v>
+        <v>2.454868651163602</v>
       </c>
       <c r="U66">
         <v>0.2358</v>
       </c>
       <c r="V66">
-        <v>0.07973715130810162</v>
+        <v>0.0785104259033616</v>
       </c>
       <c r="W66">
-        <v>0.2169979797215496</v>
+        <v>0.2172872415719874</v>
       </c>
       <c r="X66" t="inlineStr">
         <is>
@@ -7368,7 +7368,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>0.3870735500393282</v>
+        <v>0.3811185723464154</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -7376,22 +7376,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.1944702414301762</v>
+        <v>0.1963702414301761</v>
       </c>
       <c r="C67">
-        <v>-11.48545491510182</v>
+        <v>-12.63084188537663</v>
       </c>
       <c r="D67">
-        <v>36.24454508489818</v>
+        <v>35.92515811462337</v>
       </c>
       <c r="E67">
-        <v>33.09</v>
+        <v>33.916</v>
       </c>
       <c r="F67">
-        <v>53.69</v>
+        <v>54.516</v>
       </c>
       <c r="G67">
         <v>5.96</v>
@@ -7412,37 +7412,37 @@
         <v>4.824999999999999</v>
       </c>
       <c r="M67">
-        <v>12.660102</v>
+        <v>12.8548728</v>
       </c>
       <c r="N67">
-        <v>-7.835102000000001</v>
+        <v>-8.029872800000001</v>
       </c>
       <c r="O67">
-        <v>-1.614031012</v>
+        <v>-1.6541537968</v>
       </c>
       <c r="P67">
-        <v>-6.221070988000001</v>
+        <v>-6.375719003200001</v>
       </c>
       <c r="Q67">
-        <v>3.078929012</v>
+        <v>2.924280996799999</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.1520958125953839</v>
+        <v>0.1552221600246599</v>
       </c>
       <c r="T67">
-        <v>2.454868651163602</v>
+        <v>2.527070670315472</v>
       </c>
       <c r="U67">
         <v>0.2358</v>
       </c>
       <c r="V67">
-        <v>0.0785104259033616</v>
+        <v>0.0773208739957349</v>
       </c>
       <c r="W67">
-        <v>0.2172872415719874</v>
+        <v>0.2175677379118057</v>
       </c>
       <c r="X67" t="inlineStr">
         <is>
@@ -7450,7 +7450,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>0.3811185723464154</v>
+        <v>0.3753440485229849</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -7458,22 +7458,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.1963702414301761</v>
+        <v>0.1982702414301762</v>
       </c>
       <c r="C68">
-        <v>-12.63084188537663</v>
+        <v>-13.77064914739537</v>
       </c>
       <c r="D68">
-        <v>35.92515811462337</v>
+        <v>35.61135085260463</v>
       </c>
       <c r="E68">
-        <v>33.916</v>
+        <v>34.742</v>
       </c>
       <c r="F68">
-        <v>54.516</v>
+        <v>55.342</v>
       </c>
       <c r="G68">
         <v>5.96</v>
@@ -7494,37 +7494,37 @@
         <v>4.824999999999999</v>
       </c>
       <c r="M68">
-        <v>12.8548728</v>
+        <v>13.0496436</v>
       </c>
       <c r="N68">
-        <v>-8.029872800000001</v>
+        <v>-8.2246436</v>
       </c>
       <c r="O68">
-        <v>-1.6541537968</v>
+        <v>-1.6942765816</v>
       </c>
       <c r="P68">
-        <v>-6.375719003200001</v>
+        <v>-6.5303670184</v>
       </c>
       <c r="Q68">
-        <v>2.924280996799999</v>
+        <v>2.769632981600001</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.1552221600246599</v>
+        <v>0.1585379830557102</v>
       </c>
       <c r="T68">
-        <v>2.527070670315472</v>
+        <v>2.603648569415941</v>
       </c>
       <c r="U68">
         <v>0.2358</v>
       </c>
       <c r="V68">
-        <v>0.0773208739957349</v>
+        <v>0.07616683110027618</v>
       </c>
       <c r="W68">
-        <v>0.2175677379118057</v>
+        <v>0.2178398612265549</v>
       </c>
       <c r="X68" t="inlineStr">
         <is>
@@ -7532,7 +7532,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>0.3753440485229849</v>
+        <v>0.3697418985450299</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -7540,22 +7540,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.1982702414301762</v>
+        <v>0.2001702414301761</v>
       </c>
       <c r="C69">
-        <v>-13.77064914739537</v>
+        <v>-14.90502165173422</v>
       </c>
       <c r="D69">
-        <v>35.61135085260463</v>
+        <v>35.30297834826577</v>
       </c>
       <c r="E69">
-        <v>34.742</v>
+        <v>35.568</v>
       </c>
       <c r="F69">
-        <v>55.342</v>
+        <v>56.168</v>
       </c>
       <c r="G69">
         <v>5.96</v>
@@ -7576,37 +7576,37 @@
         <v>4.824999999999999</v>
       </c>
       <c r="M69">
-        <v>13.0496436</v>
+        <v>13.2444144</v>
       </c>
       <c r="N69">
-        <v>-8.2246436</v>
+        <v>-8.419414400000001</v>
       </c>
       <c r="O69">
-        <v>-1.6942765816</v>
+        <v>-1.7343993664</v>
       </c>
       <c r="P69">
-        <v>-6.5303670184</v>
+        <v>-6.685015033600001</v>
       </c>
       <c r="Q69">
-        <v>2.769632981600001</v>
+        <v>2.6149849664</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.1585379830557102</v>
+        <v>0.1620610450262012</v>
       </c>
       <c r="T69">
-        <v>2.603648569415941</v>
+        <v>2.685012587210189</v>
       </c>
       <c r="U69">
         <v>0.2358</v>
       </c>
       <c r="V69">
-        <v>0.07616683110027618</v>
+        <v>0.07504673064291917</v>
       </c>
       <c r="W69">
-        <v>0.2178398612265549</v>
+        <v>0.2181039809143996</v>
       </c>
       <c r="X69" t="inlineStr">
         <is>
@@ -7614,7 +7614,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>0.3697418985450299</v>
+        <v>0.3643045176840736</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -7622,22 +7622,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.2001702414301761</v>
+        <v>0.2020702414301762</v>
       </c>
       <c r="C70">
-        <v>-14.90502165173422</v>
+        <v>-16.03409937133952</v>
       </c>
       <c r="D70">
-        <v>35.30297834826577</v>
+        <v>34.99990062866048</v>
       </c>
       <c r="E70">
-        <v>35.568</v>
+        <v>36.394</v>
       </c>
       <c r="F70">
-        <v>56.168</v>
+        <v>56.994</v>
       </c>
       <c r="G70">
         <v>5.96</v>
@@ -7658,37 +7658,37 @@
         <v>4.824999999999999</v>
       </c>
       <c r="M70">
-        <v>13.2444144</v>
+        <v>13.4391852</v>
       </c>
       <c r="N70">
-        <v>-8.419414400000001</v>
+        <v>-8.614185200000001</v>
       </c>
       <c r="O70">
-        <v>-1.7343993664</v>
+        <v>-1.7745221512</v>
       </c>
       <c r="P70">
-        <v>-6.685015033600001</v>
+        <v>-6.839663048800001</v>
       </c>
       <c r="Q70">
-        <v>2.6149849664</v>
+        <v>2.4603369512</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.1620610450262012</v>
+        <v>0.165811401317369</v>
       </c>
       <c r="T70">
-        <v>2.685012587210189</v>
+        <v>2.771625896475034</v>
       </c>
       <c r="U70">
         <v>0.2358</v>
       </c>
       <c r="V70">
-        <v>0.07504673064291917</v>
+        <v>0.07395909686548556</v>
       </c>
       <c r="W70">
-        <v>0.2181039809143996</v>
+        <v>0.2183604449591185</v>
       </c>
       <c r="X70" t="inlineStr">
         <is>
@@ -7696,7 +7696,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>0.3643045176840736</v>
+        <v>0.3590247420654639</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7704,22 +7704,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.2020702414301762</v>
+        <v>0.2039702414301762</v>
       </c>
       <c r="C71">
-        <v>-16.03409937133952</v>
+        <v>-17.15801751337486</v>
       </c>
       <c r="D71">
-        <v>34.99990062866048</v>
+        <v>34.70198248662514</v>
       </c>
       <c r="E71">
-        <v>36.394</v>
+        <v>37.22</v>
       </c>
       <c r="F71">
-        <v>56.994</v>
+        <v>57.82</v>
       </c>
       <c r="G71">
         <v>5.96</v>
@@ -7740,37 +7740,37 @@
         <v>4.824999999999999</v>
       </c>
       <c r="M71">
-        <v>13.4391852</v>
+        <v>13.633956</v>
       </c>
       <c r="N71">
-        <v>-8.614185200000001</v>
+        <v>-8.808956000000002</v>
       </c>
       <c r="O71">
-        <v>-1.7745221512</v>
+        <v>-1.814644936000001</v>
       </c>
       <c r="P71">
-        <v>-6.839663048800001</v>
+        <v>-6.994311064000001</v>
       </c>
       <c r="Q71">
-        <v>2.4603369512</v>
+        <v>2.305688935999999</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.165811401317369</v>
+        <v>0.1698117813612812</v>
       </c>
       <c r="T71">
-        <v>2.771625896475034</v>
+        <v>2.864013426357535</v>
       </c>
       <c r="U71">
         <v>0.2358</v>
       </c>
       <c r="V71">
-        <v>0.07395909686548556</v>
+        <v>0.07290253833883577</v>
       </c>
       <c r="W71">
-        <v>0.2183604449591185</v>
+        <v>0.2186095814597026</v>
       </c>
       <c r="X71" t="inlineStr">
         <is>
@@ -7778,7 +7778,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>0.3590247420654639</v>
+        <v>0.3538958171788144</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7786,22 +7786,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.2039702414301762</v>
+        <v>0.2058702414301762</v>
       </c>
       <c r="C72">
-        <v>-17.15801751337486</v>
+        <v>-18.27690672034028</v>
       </c>
       <c r="D72">
-        <v>34.70198248662514</v>
+        <v>34.40909327965972</v>
       </c>
       <c r="E72">
-        <v>37.22</v>
+        <v>38.046</v>
       </c>
       <c r="F72">
-        <v>57.82</v>
+        <v>58.646</v>
       </c>
       <c r="G72">
         <v>5.96</v>
@@ -7822,37 +7822,37 @@
         <v>4.824999999999999</v>
       </c>
       <c r="M72">
-        <v>13.633956</v>
+        <v>13.8287268</v>
       </c>
       <c r="N72">
-        <v>-8.808956000000002</v>
+        <v>-9.003726800000001</v>
       </c>
       <c r="O72">
-        <v>-1.814644936000001</v>
+        <v>-1.8547677208</v>
       </c>
       <c r="P72">
-        <v>-6.994311064000001</v>
+        <v>-7.148959079200001</v>
       </c>
       <c r="Q72">
-        <v>2.305688935999999</v>
+        <v>2.1510409208</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.1698117813612812</v>
+        <v>0.1740880496840841</v>
       </c>
       <c r="T72">
-        <v>2.864013426357535</v>
+        <v>2.962772510025037</v>
       </c>
       <c r="U72">
         <v>0.2358</v>
       </c>
       <c r="V72">
-        <v>0.07290253833883577</v>
+        <v>0.07187574202420427</v>
       </c>
       <c r="W72">
-        <v>0.2186095814597026</v>
+        <v>0.2188517000306927</v>
       </c>
       <c r="X72" t="inlineStr">
         <is>
@@ -7860,7 +7860,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>0.3538958171788144</v>
+        <v>0.3489113690495353</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7868,22 +7868,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.2058702414301761</v>
+        <v>0.2077702414301761</v>
       </c>
       <c r="C73">
-        <v>-18.27690672034026</v>
+        <v>-19.39089326109173</v>
       </c>
       <c r="D73">
-        <v>34.40909327965973</v>
+        <v>34.12110673890826</v>
       </c>
       <c r="E73">
-        <v>38.04599999999999</v>
+        <v>38.87199999999999</v>
       </c>
       <c r="F73">
-        <v>58.64599999999999</v>
+        <v>59.47199999999999</v>
       </c>
       <c r="G73">
         <v>5.96</v>
@@ -7904,37 +7904,37 @@
         <v>4.824999999999999</v>
       </c>
       <c r="M73">
-        <v>13.8287268</v>
+        <v>14.0234976</v>
       </c>
       <c r="N73">
-        <v>-9.003726799999999</v>
+        <v>-9.1984976</v>
       </c>
       <c r="O73">
-        <v>-1.8547677208</v>
+        <v>-1.8948905056</v>
       </c>
       <c r="P73">
-        <v>-7.148959079199999</v>
+        <v>-7.303607094399999</v>
       </c>
       <c r="Q73">
-        <v>2.151040920800002</v>
+        <v>1.996392905600001</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.1740880496840841</v>
+        <v>0.1786697657442299</v>
       </c>
       <c r="T73">
-        <v>2.962772510025036</v>
+        <v>3.068585813954501</v>
       </c>
       <c r="U73">
         <v>0.2358</v>
       </c>
       <c r="V73">
-        <v>0.07187574202420428</v>
+        <v>0.07087746782942367</v>
       </c>
       <c r="W73">
-        <v>0.2188517000306926</v>
+        <v>0.2190870930858219</v>
       </c>
       <c r="X73" t="inlineStr">
         <is>
@@ -7942,7 +7942,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>0.3489113690495353</v>
+        <v>0.3440653778127363</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7950,22 +7950,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.2077702414301761</v>
+        <v>0.2096702414301761</v>
       </c>
       <c r="C74">
-        <v>-19.39089326109173</v>
+        <v>-20.50009921234788</v>
       </c>
       <c r="D74">
-        <v>34.12110673890826</v>
+        <v>33.83790078765212</v>
       </c>
       <c r="E74">
-        <v>38.87199999999999</v>
+        <v>39.69799999999999</v>
       </c>
       <c r="F74">
-        <v>59.47199999999999</v>
+        <v>60.29799999999999</v>
       </c>
       <c r="G74">
         <v>5.96</v>
@@ -7986,37 +7986,37 @@
         <v>4.824999999999999</v>
       </c>
       <c r="M74">
-        <v>14.0234976</v>
+        <v>14.2182684</v>
       </c>
       <c r="N74">
-        <v>-9.1984976</v>
+        <v>-9.3932684</v>
       </c>
       <c r="O74">
-        <v>-1.8948905056</v>
+        <v>-1.9350132904</v>
       </c>
       <c r="P74">
-        <v>-7.303607094399999</v>
+        <v>-7.4582551096</v>
       </c>
       <c r="Q74">
-        <v>1.996392905600001</v>
+        <v>1.841744890400001</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.1786697657442299</v>
+        <v>0.1835908681792014</v>
       </c>
       <c r="T74">
-        <v>3.068585813954501</v>
+        <v>3.18223714039726</v>
       </c>
       <c r="U74">
         <v>0.2358</v>
       </c>
       <c r="V74">
-        <v>0.07087746782942367</v>
+        <v>0.06990654361258225</v>
       </c>
       <c r="W74">
-        <v>0.2190870930858219</v>
+        <v>0.2193160370161531</v>
       </c>
       <c r="X74" t="inlineStr">
         <is>
@@ -8024,7 +8024,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>0.3440653778127363</v>
+        <v>0.3393521534591371</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -8032,22 +8032,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.2096702414301761</v>
+        <v>0.2115702414301761</v>
       </c>
       <c r="C75">
-        <v>-20.50009921234788</v>
+        <v>-21.60464263123203</v>
       </c>
       <c r="D75">
-        <v>33.83790078765212</v>
+        <v>33.55935736876796</v>
       </c>
       <c r="E75">
-        <v>39.69799999999999</v>
+        <v>40.52399999999999</v>
       </c>
       <c r="F75">
-        <v>60.29799999999999</v>
+        <v>61.124</v>
       </c>
       <c r="G75">
         <v>5.96</v>
@@ -8068,37 +8068,37 @@
         <v>4.824999999999999</v>
       </c>
       <c r="M75">
-        <v>14.2182684</v>
+        <v>14.4130392</v>
       </c>
       <c r="N75">
-        <v>-9.3932684</v>
+        <v>-9.588039200000001</v>
       </c>
       <c r="O75">
-        <v>-1.9350132904</v>
+        <v>-1.9751360752</v>
       </c>
       <c r="P75">
-        <v>-7.4582551096</v>
+        <v>-7.612903124800001</v>
       </c>
       <c r="Q75">
-        <v>1.841744890400001</v>
+        <v>1.6870968752</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.1835908681792014</v>
+        <v>0.1888905169553245</v>
       </c>
       <c r="T75">
-        <v>3.18223714039726</v>
+        <v>3.304630876566386</v>
       </c>
       <c r="U75">
         <v>0.2358</v>
       </c>
       <c r="V75">
-        <v>0.06990654361258225</v>
+        <v>0.0689618605907906</v>
       </c>
       <c r="W75">
-        <v>0.2193160370161531</v>
+        <v>0.2195387932726916</v>
       </c>
       <c r="X75" t="inlineStr">
         <is>
@@ -8106,7 +8106,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>0.3393521534591371</v>
+        <v>0.3347663135475271</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -8114,22 +8114,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.2115702414301761</v>
+        <v>0.2134702414301761</v>
       </c>
       <c r="C76">
-        <v>-21.60464263123203</v>
+        <v>-22.70463771936203</v>
       </c>
       <c r="D76">
-        <v>33.55935736876796</v>
+        <v>33.28536228063797</v>
       </c>
       <c r="E76">
-        <v>40.52399999999999</v>
+        <v>41.34999999999999</v>
       </c>
       <c r="F76">
-        <v>61.124</v>
+        <v>61.95</v>
       </c>
       <c r="G76">
         <v>5.96</v>
@@ -8150,37 +8150,37 @@
         <v>4.824999999999999</v>
       </c>
       <c r="M76">
-        <v>14.4130392</v>
+        <v>14.60781</v>
       </c>
       <c r="N76">
-        <v>-9.588039200000001</v>
+        <v>-9.78281</v>
       </c>
       <c r="O76">
-        <v>-1.9751360752</v>
+        <v>-2.01525886</v>
       </c>
       <c r="P76">
-        <v>-7.612903124800001</v>
+        <v>-7.76755114</v>
       </c>
       <c r="Q76">
-        <v>1.6870968752</v>
+        <v>1.532448860000001</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.1888905169553245</v>
+        <v>0.1946141376335375</v>
       </c>
       <c r="T76">
-        <v>3.304630876566386</v>
+        <v>3.436816111629041</v>
       </c>
       <c r="U76">
         <v>0.2358</v>
       </c>
       <c r="V76">
-        <v>0.0689618605907906</v>
+        <v>0.06804236911624673</v>
       </c>
       <c r="W76">
-        <v>0.2195387932726916</v>
+        <v>0.219755609362389</v>
       </c>
       <c r="X76" t="inlineStr">
         <is>
@@ -8188,7 +8188,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>0.3347663135475271</v>
+        <v>0.3303027627002267</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -8196,22 +8196,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.2134702414301761</v>
+        <v>0.2153702414301761</v>
       </c>
       <c r="C77">
-        <v>-22.70463771936203</v>
+        <v>-23.80019497896675</v>
       </c>
       <c r="D77">
-        <v>33.28536228063797</v>
+        <v>33.01580502103324</v>
       </c>
       <c r="E77">
-        <v>41.34999999999999</v>
+        <v>42.17599999999999</v>
       </c>
       <c r="F77">
-        <v>61.95</v>
+        <v>62.776</v>
       </c>
       <c r="G77">
         <v>5.96</v>
@@ -8232,37 +8232,37 @@
         <v>4.824999999999999</v>
       </c>
       <c r="M77">
-        <v>14.60781</v>
+        <v>14.8025808</v>
       </c>
       <c r="N77">
-        <v>-9.78281</v>
+        <v>-9.9775808</v>
       </c>
       <c r="O77">
-        <v>-2.01525886</v>
+        <v>-2.0553816448</v>
       </c>
       <c r="P77">
-        <v>-7.76755114</v>
+        <v>-7.9221991552</v>
       </c>
       <c r="Q77">
-        <v>1.532448860000001</v>
+        <v>1.377800844800001</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.1946141376335375</v>
+        <v>0.2008147267016016</v>
       </c>
       <c r="T77">
-        <v>3.436816111629041</v>
+        <v>3.580016782946918</v>
       </c>
       <c r="U77">
         <v>0.2358</v>
       </c>
       <c r="V77">
-        <v>0.06804236911624673</v>
+        <v>0.0671470747857698</v>
       </c>
       <c r="W77">
-        <v>0.219755609362389</v>
+        <v>0.2199667197655155</v>
       </c>
       <c r="X77" t="inlineStr">
         <is>
@@ -8270,7 +8270,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>0.3303027627002267</v>
+        <v>0.3259566737173291</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -8278,22 +8278,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.2153702414301761</v>
+        <v>0.2172702414301761</v>
       </c>
       <c r="C78">
-        <v>-23.80019497896675</v>
+        <v>-24.89142136147797</v>
       </c>
       <c r="D78">
-        <v>33.01580502103324</v>
+        <v>32.75057863852203</v>
       </c>
       <c r="E78">
-        <v>42.17599999999999</v>
+        <v>43.002</v>
       </c>
       <c r="F78">
-        <v>62.776</v>
+        <v>63.602</v>
       </c>
       <c r="G78">
         <v>5.96</v>
@@ -8314,37 +8314,37 @@
         <v>4.824999999999999</v>
       </c>
       <c r="M78">
-        <v>14.8025808</v>
+        <v>14.9973516</v>
       </c>
       <c r="N78">
-        <v>-9.9775808</v>
+        <v>-10.1723516</v>
       </c>
       <c r="O78">
-        <v>-2.0553816448</v>
+        <v>-2.0955044296</v>
       </c>
       <c r="P78">
-        <v>-7.9221991552</v>
+        <v>-8.076847170400001</v>
       </c>
       <c r="Q78">
-        <v>1.377800844800001</v>
+        <v>1.2231528296</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.2008147267016016</v>
+        <v>0.2075544974277582</v>
       </c>
       <c r="T78">
-        <v>3.580016782946918</v>
+        <v>3.735669686553306</v>
       </c>
       <c r="U78">
         <v>0.2358</v>
       </c>
       <c r="V78">
-        <v>0.0671470747857698</v>
+        <v>0.06627503485348707</v>
       </c>
       <c r="W78">
-        <v>0.2199667197655155</v>
+        <v>0.2201723467815478</v>
       </c>
       <c r="X78" t="inlineStr">
         <is>
@@ -8352,7 +8352,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>0.3259566737173291</v>
+        <v>0.3217234701625585</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -8360,22 +8360,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.2172702414301761</v>
+        <v>0.2191702414301762</v>
       </c>
       <c r="C79">
-        <v>-24.89142136147797</v>
+        <v>-25.97842040901708</v>
       </c>
       <c r="D79">
-        <v>32.75057863852203</v>
+        <v>32.48957959098291</v>
       </c>
       <c r="E79">
-        <v>43.002</v>
+        <v>43.828</v>
       </c>
       <c r="F79">
-        <v>63.602</v>
+        <v>64.428</v>
       </c>
       <c r="G79">
         <v>5.96</v>
@@ -8396,37 +8396,37 @@
         <v>4.824999999999999</v>
       </c>
       <c r="M79">
-        <v>14.9973516</v>
+        <v>15.1921224</v>
       </c>
       <c r="N79">
-        <v>-10.1723516</v>
+        <v>-10.3671224</v>
       </c>
       <c r="O79">
-        <v>-2.0955044296</v>
+        <v>-2.1356272144</v>
       </c>
       <c r="P79">
-        <v>-8.076847170400001</v>
+        <v>-8.2314951856</v>
       </c>
       <c r="Q79">
-        <v>1.2231528296</v>
+        <v>1.068504814400001</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.2075544974277582</v>
+        <v>0.2149069745835653</v>
       </c>
       <c r="T79">
-        <v>3.735669686553306</v>
+        <v>3.905472854123911</v>
       </c>
       <c r="U79">
         <v>0.2358</v>
       </c>
       <c r="V79">
-        <v>0.06627503485348707</v>
+        <v>0.06542535491946799</v>
       </c>
       <c r="W79">
-        <v>0.2201723467815478</v>
+        <v>0.2203727013099895</v>
       </c>
       <c r="X79" t="inlineStr">
         <is>
@@ -8434,7 +8434,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>0.3217234701625585</v>
+        <v>0.3175988102886795</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -8442,22 +8442,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.2191702414301762</v>
+        <v>0.2210702414301761</v>
       </c>
       <c r="C80">
-        <v>-25.97842040901708</v>
+        <v>-27.06129238917007</v>
       </c>
       <c r="D80">
-        <v>32.48957959098291</v>
+        <v>32.23270761082993</v>
       </c>
       <c r="E80">
-        <v>43.828</v>
+        <v>44.654</v>
       </c>
       <c r="F80">
-        <v>64.428</v>
+        <v>65.254</v>
       </c>
       <c r="G80">
         <v>5.96</v>
@@ -8478,37 +8478,37 @@
         <v>4.824999999999999</v>
       </c>
       <c r="M80">
-        <v>15.1921224</v>
+        <v>15.3868932</v>
       </c>
       <c r="N80">
-        <v>-10.3671224</v>
+        <v>-10.5618932</v>
       </c>
       <c r="O80">
-        <v>-2.1356272144</v>
+        <v>-2.175749999200001</v>
       </c>
       <c r="P80">
-        <v>-8.2314951856</v>
+        <v>-8.386143200800001</v>
       </c>
       <c r="Q80">
-        <v>1.068504814400001</v>
+        <v>0.9138567991999995</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.2149069745835653</v>
+        <v>0.2229596876589733</v>
       </c>
       <c r="T80">
-        <v>3.905472854123911</v>
+        <v>4.091447751939336</v>
       </c>
       <c r="U80">
         <v>0.2358</v>
       </c>
       <c r="V80">
-        <v>0.06542535491946799</v>
+        <v>0.06459718586985448</v>
       </c>
       <c r="W80">
-        <v>0.2203727013099895</v>
+        <v>0.2205679835718883</v>
       </c>
       <c r="X80" t="inlineStr">
         <is>
@@ -8516,7 +8516,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>0.3175988102886795</v>
+        <v>0.3135785721837595</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -8524,22 +8524,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.2210702414301761</v>
+        <v>0.2229702414301762</v>
       </c>
       <c r="C81">
-        <v>-27.06129238917007</v>
+        <v>-28.14013442341918</v>
       </c>
       <c r="D81">
-        <v>32.23270761082993</v>
+        <v>31.97986557658082</v>
       </c>
       <c r="E81">
-        <v>44.654</v>
+        <v>45.48</v>
       </c>
       <c r="F81">
-        <v>65.254</v>
+        <v>66.08</v>
       </c>
       <c r="G81">
         <v>5.96</v>
@@ -8560,37 +8560,37 @@
         <v>4.824999999999999</v>
       </c>
       <c r="M81">
-        <v>15.3868932</v>
+        <v>15.581664</v>
       </c>
       <c r="N81">
-        <v>-10.5618932</v>
+        <v>-10.756664</v>
       </c>
       <c r="O81">
-        <v>-2.175749999200001</v>
+        <v>-2.215872784</v>
       </c>
       <c r="P81">
-        <v>-8.386143200800001</v>
+        <v>-8.540791216000001</v>
       </c>
       <c r="Q81">
-        <v>0.9138567991999995</v>
+        <v>0.7592087840000001</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.2229596876589733</v>
+        <v>0.2318176720419219</v>
       </c>
       <c r="T81">
-        <v>4.091447751939336</v>
+        <v>4.296020139536303</v>
       </c>
       <c r="U81">
         <v>0.2358</v>
       </c>
       <c r="V81">
-        <v>0.06459718586985448</v>
+        <v>0.0637897210464813</v>
       </c>
       <c r="W81">
-        <v>0.2205679835718883</v>
+        <v>0.2207583837772397</v>
       </c>
       <c r="X81" t="inlineStr">
         <is>
@@ -8598,7 +8598,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>0.3135785721837595</v>
+        <v>0.3096588400314626</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -8606,22 +8606,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.2229702414301762</v>
+        <v>0.2248702414301762</v>
       </c>
       <c r="C82">
-        <v>-28.14013442341918</v>
+        <v>-29.21504060957697</v>
       </c>
       <c r="D82">
-        <v>31.97986557658082</v>
+        <v>31.73095939042303</v>
       </c>
       <c r="E82">
-        <v>45.48</v>
+        <v>46.306</v>
       </c>
       <c r="F82">
-        <v>66.08</v>
+        <v>66.90600000000001</v>
       </c>
       <c r="G82">
         <v>5.96</v>
@@ -8642,37 +8642,37 @@
         <v>4.824999999999999</v>
       </c>
       <c r="M82">
-        <v>15.581664</v>
+        <v>15.7764348</v>
       </c>
       <c r="N82">
-        <v>-10.756664</v>
+        <v>-10.9514348</v>
       </c>
       <c r="O82">
-        <v>-2.215872784</v>
+        <v>-2.255995568800001</v>
       </c>
       <c r="P82">
-        <v>-8.540791216000001</v>
+        <v>-8.695439231200002</v>
       </c>
       <c r="Q82">
-        <v>0.7592087840000001</v>
+        <v>0.604560768799999</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.2318176720419219</v>
+        <v>0.2416080758336021</v>
       </c>
       <c r="T82">
-        <v>4.296020139536303</v>
+        <v>4.522126462669793</v>
       </c>
       <c r="U82">
         <v>0.2358</v>
       </c>
       <c r="V82">
-        <v>0.0637897210464813</v>
+        <v>0.06300219362615435</v>
       </c>
       <c r="W82">
-        <v>0.2207583837772397</v>
+        <v>0.2209440827429528</v>
       </c>
       <c r="X82" t="inlineStr">
         <is>
@@ -8680,7 +8680,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>0.3096588400314626</v>
+        <v>0.3058358913890988</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8688,22 +8688,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.2248702414301762</v>
+        <v>0.2267702414301762</v>
       </c>
       <c r="C83">
-        <v>-29.21504060957697</v>
+        <v>-30.28610213854684</v>
       </c>
       <c r="D83">
-        <v>31.73095939042303</v>
+        <v>31.48589786145315</v>
       </c>
       <c r="E83">
-        <v>46.306</v>
+        <v>47.132</v>
       </c>
       <c r="F83">
-        <v>66.90600000000001</v>
+        <v>67.732</v>
       </c>
       <c r="G83">
         <v>5.96</v>
@@ -8724,37 +8724,37 @@
         <v>4.824999999999999</v>
       </c>
       <c r="M83">
-        <v>15.7764348</v>
+        <v>15.9712056</v>
       </c>
       <c r="N83">
-        <v>-10.9514348</v>
+        <v>-11.1462056</v>
       </c>
       <c r="O83">
-        <v>-2.255995568800001</v>
+        <v>-2.296118353600001</v>
       </c>
       <c r="P83">
-        <v>-8.695439231200002</v>
+        <v>-8.850087246400001</v>
       </c>
       <c r="Q83">
-        <v>0.604560768799999</v>
+        <v>0.4499127535999996</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.2416080758336021</v>
+        <v>0.2524863022688021</v>
       </c>
       <c r="T83">
-        <v>4.522126462669793</v>
+        <v>4.773355710595892</v>
       </c>
       <c r="U83">
         <v>0.2358</v>
       </c>
       <c r="V83">
-        <v>0.06300219362615435</v>
+        <v>0.06223387419168906</v>
       </c>
       <c r="W83">
-        <v>0.2209440827429528</v>
+        <v>0.2211252524655997</v>
       </c>
       <c r="X83" t="inlineStr">
         <is>
@@ -8762,7 +8762,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>0.3058358913890988</v>
+        <v>0.3021061853965489</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8770,22 +8770,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.2267702414301762</v>
+        <v>0.2286702414301762</v>
       </c>
       <c r="C84">
-        <v>-30.28610213854684</v>
+        <v>-31.35340740571464</v>
       </c>
       <c r="D84">
-        <v>31.48589786145315</v>
+        <v>31.24459259428537</v>
       </c>
       <c r="E84">
-        <v>47.132</v>
+        <v>47.95800000000001</v>
       </c>
       <c r="F84">
-        <v>67.732</v>
+        <v>68.55800000000001</v>
       </c>
       <c r="G84">
         <v>5.96</v>
@@ -8806,37 +8806,37 @@
         <v>4.824999999999999</v>
       </c>
       <c r="M84">
-        <v>15.9712056</v>
+        <v>16.1659764</v>
       </c>
       <c r="N84">
-        <v>-11.1462056</v>
+        <v>-11.3409764</v>
       </c>
       <c r="O84">
-        <v>-2.296118353600001</v>
+        <v>-2.336241138400001</v>
       </c>
       <c r="P84">
-        <v>-8.850087246400001</v>
+        <v>-9.004735261600002</v>
       </c>
       <c r="Q84">
-        <v>0.4499127535999996</v>
+        <v>0.2952647383999984</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.2524863022688021</v>
+        <v>0.2646443200493199</v>
       </c>
       <c r="T84">
-        <v>4.773355710595892</v>
+        <v>5.054141340630945</v>
       </c>
       <c r="U84">
         <v>0.2358</v>
       </c>
       <c r="V84">
-        <v>0.06223387419168906</v>
+        <v>0.06148406847853619</v>
       </c>
       <c r="W84">
-        <v>0.2211252524655997</v>
+        <v>0.2213020566527612</v>
       </c>
       <c r="X84" t="inlineStr">
         <is>
@@ -8844,7 +8844,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>0.3021061853965489</v>
+        <v>0.2984663518375542</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8852,22 +8852,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.2286702414301762</v>
+        <v>0.2305702414301762</v>
       </c>
       <c r="C85">
-        <v>-31.35340740571464</v>
+        <v>-32.4170421172569</v>
       </c>
       <c r="D85">
-        <v>31.24459259428537</v>
+        <v>31.00695788274311</v>
       </c>
       <c r="E85">
-        <v>47.95800000000001</v>
+        <v>48.784</v>
       </c>
       <c r="F85">
-        <v>68.55800000000001</v>
+        <v>69.384</v>
       </c>
       <c r="G85">
         <v>5.96</v>
@@ -8888,37 +8888,37 @@
         <v>4.824999999999999</v>
       </c>
       <c r="M85">
-        <v>16.1659764</v>
+        <v>16.3607472</v>
       </c>
       <c r="N85">
-        <v>-11.3409764</v>
+        <v>-11.5357472</v>
       </c>
       <c r="O85">
-        <v>-2.336241138400001</v>
+        <v>-2.376363923200001</v>
       </c>
       <c r="P85">
-        <v>-9.004735261600002</v>
+        <v>-9.159383276800002</v>
       </c>
       <c r="Q85">
-        <v>0.2952647383999984</v>
+        <v>0.1406167231999991</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.2646443200493199</v>
+        <v>0.2783220900524025</v>
       </c>
       <c r="T85">
-        <v>5.054141340630945</v>
+        <v>5.370025174420381</v>
       </c>
       <c r="U85">
         <v>0.2358</v>
       </c>
       <c r="V85">
-        <v>0.06148406847853619</v>
+        <v>0.06075211528236313</v>
       </c>
       <c r="W85">
-        <v>0.2213020566527612</v>
+        <v>0.2214746512164188</v>
       </c>
       <c r="X85" t="inlineStr">
         <is>
@@ -8926,7 +8926,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>0.2984663518375542</v>
+        <v>0.2949131809823453</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8934,22 +8934,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.2305702414301762</v>
+        <v>0.2324702414301761</v>
       </c>
       <c r="C86">
-        <v>-32.41704211725688</v>
+        <v>-33.47708939163461</v>
       </c>
       <c r="D86">
-        <v>31.00695788274311</v>
+        <v>30.77291060836539</v>
       </c>
       <c r="E86">
-        <v>48.78399999999998</v>
+        <v>49.60999999999999</v>
       </c>
       <c r="F86">
-        <v>69.38399999999999</v>
+        <v>70.20999999999999</v>
       </c>
       <c r="G86">
         <v>5.96</v>
@@ -8970,37 +8970,37 @@
         <v>4.824999999999999</v>
       </c>
       <c r="M86">
-        <v>16.3607472</v>
+        <v>16.555518</v>
       </c>
       <c r="N86">
-        <v>-11.5357472</v>
+        <v>-11.730518</v>
       </c>
       <c r="O86">
-        <v>-2.3763639232</v>
+        <v>-2.416486708</v>
       </c>
       <c r="P86">
-        <v>-9.1593832768</v>
+        <v>-9.314031291999999</v>
       </c>
       <c r="Q86">
-        <v>0.1406167232000008</v>
+        <v>-0.01403129199999853</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>0.2783220900524023</v>
+        <v>0.2938235627225625</v>
       </c>
       <c r="T86">
-        <v>5.370025174420377</v>
+        <v>5.728026852715069</v>
       </c>
       <c r="U86">
         <v>0.2358</v>
       </c>
       <c r="V86">
-        <v>0.06075211528236314</v>
+        <v>0.06003738451433534</v>
       </c>
       <c r="W86">
-        <v>0.2214746512164188</v>
+        <v>0.2216431847315197</v>
       </c>
       <c r="X86" t="inlineStr">
         <is>
@@ -9008,7 +9008,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>0.2949131809823453</v>
+        <v>0.2914436141472589</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -9016,22 +9016,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.2324702414301761</v>
+        <v>0.2343702414301762</v>
       </c>
       <c r="C87">
-        <v>-33.47708939163461</v>
+        <v>-34.53362985652471</v>
       </c>
       <c r="D87">
-        <v>30.77291060836539</v>
+        <v>30.54237014347527</v>
       </c>
       <c r="E87">
-        <v>49.60999999999999</v>
+        <v>50.43599999999999</v>
       </c>
       <c r="F87">
-        <v>70.20999999999999</v>
+        <v>71.03599999999999</v>
       </c>
       <c r="G87">
         <v>5.96</v>
@@ -9052,37 +9052,37 @@
         <v>4.824999999999999</v>
       </c>
       <c r="M87">
-        <v>16.555518</v>
+        <v>16.7502888</v>
       </c>
       <c r="N87">
-        <v>-11.730518</v>
+        <v>-11.9252888</v>
       </c>
       <c r="O87">
-        <v>-2.416486708</v>
+        <v>-2.4566094928</v>
       </c>
       <c r="P87">
-        <v>-9.314031291999999</v>
+        <v>-9.468679307199997</v>
       </c>
       <c r="Q87">
-        <v>-0.01403129199999853</v>
+        <v>-0.1686793071999961</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>0.2938235627225625</v>
+        <v>0.3115395314884598</v>
       </c>
       <c r="T87">
-        <v>5.728026852715069</v>
+        <v>6.137171627909003</v>
       </c>
       <c r="U87">
         <v>0.2358</v>
       </c>
       <c r="V87">
-        <v>0.06003738451433534</v>
+        <v>0.05933927539207563</v>
       </c>
       <c r="W87">
-        <v>0.2216431847315197</v>
+        <v>0.2218077988625486</v>
       </c>
       <c r="X87" t="inlineStr">
         <is>
@@ -9090,7 +9090,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>0.2914436141472589</v>
+        <v>0.2880547349129885</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -9098,22 +9098,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.2343702414301762</v>
+        <v>0.2362702414301762</v>
       </c>
       <c r="C88">
-        <v>-34.53362985652471</v>
+        <v>-35.58674174142701</v>
       </c>
       <c r="D88">
-        <v>30.54237014347527</v>
+        <v>30.31525825857299</v>
       </c>
       <c r="E88">
-        <v>50.43599999999999</v>
+        <v>51.26199999999999</v>
       </c>
       <c r="F88">
-        <v>71.03599999999999</v>
+        <v>71.86199999999999</v>
       </c>
       <c r="G88">
         <v>5.96</v>
@@ -9134,37 +9134,37 @@
         <v>4.824999999999999</v>
       </c>
       <c r="M88">
-        <v>16.7502888</v>
+        <v>16.9450596</v>
       </c>
       <c r="N88">
-        <v>-11.9252888</v>
+        <v>-12.1200596</v>
       </c>
       <c r="O88">
-        <v>-2.4566094928</v>
+        <v>-2.4967322776</v>
       </c>
       <c r="P88">
-        <v>-9.468679307199997</v>
+        <v>-9.623327322400002</v>
       </c>
       <c r="Q88">
-        <v>-0.1686793071999961</v>
+        <v>-0.3233273224000008</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>0.3115395314884598</v>
+        <v>0.331981033910649</v>
       </c>
       <c r="T88">
-        <v>6.137171627909003</v>
+        <v>6.609261753132771</v>
       </c>
       <c r="U88">
         <v>0.2358</v>
       </c>
       <c r="V88">
-        <v>0.05933927539207563</v>
+        <v>0.05865721475538509</v>
       </c>
       <c r="W88">
-        <v>0.2218077988625486</v>
+        <v>0.2219686287606802</v>
       </c>
       <c r="X88" t="inlineStr">
         <is>
@@ -9172,7 +9172,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>0.2880547349129885</v>
+        <v>0.2847437609484713</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -9180,22 +9180,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.2362702414301762</v>
+        <v>0.2381702414301762</v>
       </c>
       <c r="C89">
-        <v>-35.58674174142701</v>
+        <v>-36.63650096616972</v>
       </c>
       <c r="D89">
-        <v>30.31525825857299</v>
+        <v>30.09149903383028</v>
       </c>
       <c r="E89">
-        <v>51.26199999999999</v>
+        <v>52.088</v>
       </c>
       <c r="F89">
-        <v>71.86199999999999</v>
+        <v>72.688</v>
       </c>
       <c r="G89">
         <v>5.96</v>
@@ -9216,37 +9216,37 @@
         <v>4.824999999999999</v>
       </c>
       <c r="M89">
-        <v>16.9450596</v>
+        <v>17.1398304</v>
       </c>
       <c r="N89">
-        <v>-12.1200596</v>
+        <v>-12.3148304</v>
       </c>
       <c r="O89">
-        <v>-2.4967322776</v>
+        <v>-2.5368550624</v>
       </c>
       <c r="P89">
-        <v>-9.623327322400002</v>
+        <v>-9.777975337600001</v>
       </c>
       <c r="Q89">
-        <v>-0.3233273224000008</v>
+        <v>-0.4779753376000002</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>0.331981033910649</v>
+        <v>0.3558294534032032</v>
       </c>
       <c r="T89">
-        <v>6.609261753132771</v>
+        <v>7.160033565893837</v>
       </c>
       <c r="U89">
         <v>0.2358</v>
       </c>
       <c r="V89">
-        <v>0.05865721475538509</v>
+        <v>0.05799065549680118</v>
       </c>
       <c r="W89">
-        <v>0.2219686287606802</v>
+        <v>0.2221258034338543</v>
       </c>
       <c r="X89" t="inlineStr">
         <is>
@@ -9254,7 +9254,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>0.2847437609484713</v>
+        <v>0.2815080363922386</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -9262,22 +9262,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.2381702414301762</v>
+        <v>0.2400702414301761</v>
       </c>
       <c r="C90">
-        <v>-36.63650096616972</v>
+        <v>-37.68298122552428</v>
       </c>
       <c r="D90">
-        <v>30.09149903383028</v>
+        <v>29.87101877447571</v>
       </c>
       <c r="E90">
-        <v>52.088</v>
+        <v>52.91399999999999</v>
       </c>
       <c r="F90">
-        <v>72.688</v>
+        <v>73.514</v>
       </c>
       <c r="G90">
         <v>5.96</v>
@@ -9298,37 +9298,37 @@
         <v>4.824999999999999</v>
       </c>
       <c r="M90">
-        <v>17.1398304</v>
+        <v>17.3346012</v>
       </c>
       <c r="N90">
-        <v>-12.3148304</v>
+        <v>-12.5096012</v>
       </c>
       <c r="O90">
-        <v>-2.5368550624</v>
+        <v>-2.5769778472</v>
       </c>
       <c r="P90">
-        <v>-9.777975337600001</v>
+        <v>-9.932623352799999</v>
       </c>
       <c r="Q90">
-        <v>-0.4779753376000002</v>
+        <v>-0.6326233527999978</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>0.3558294534032032</v>
+        <v>0.3840139491671307</v>
       </c>
       <c r="T90">
-        <v>7.160033565893837</v>
+        <v>7.810945708247822</v>
       </c>
       <c r="U90">
         <v>0.2358</v>
       </c>
       <c r="V90">
-        <v>0.05799065549680118</v>
+        <v>0.05733907509796072</v>
       </c>
       <c r="W90">
-        <v>0.2221258034338543</v>
+        <v>0.2222794460919009</v>
       </c>
       <c r="X90" t="inlineStr">
         <is>
@@ -9336,7 +9336,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>0.2815080363922386</v>
+        <v>0.2783450247473821</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -9344,22 +9344,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.2400702414301761</v>
+        <v>0.2419702414301761</v>
       </c>
       <c r="C91">
-        <v>-37.68298122552428</v>
+        <v>-38.72625407012744</v>
       </c>
       <c r="D91">
-        <v>29.87101877447571</v>
+        <v>29.65374592987257</v>
       </c>
       <c r="E91">
-        <v>52.91399999999999</v>
+        <v>53.74</v>
       </c>
       <c r="F91">
-        <v>73.514</v>
+        <v>74.34</v>
       </c>
       <c r="G91">
         <v>5.96</v>
@@ -9380,37 +9380,37 @@
         <v>4.824999999999999</v>
       </c>
       <c r="M91">
-        <v>17.3346012</v>
+        <v>17.529372</v>
       </c>
       <c r="N91">
-        <v>-12.5096012</v>
+        <v>-12.704372</v>
       </c>
       <c r="O91">
-        <v>-2.5769778472</v>
+        <v>-2.617100632000001</v>
       </c>
       <c r="P91">
-        <v>-9.932623352799999</v>
+        <v>-10.087271368</v>
       </c>
       <c r="Q91">
-        <v>-0.6326233527999978</v>
+        <v>-0.7872713680000007</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>0.3840139491671307</v>
+        <v>0.4178353440838438</v>
       </c>
       <c r="T91">
-        <v>7.810945708247822</v>
+        <v>8.592040279072606</v>
       </c>
       <c r="U91">
         <v>0.2358</v>
       </c>
       <c r="V91">
-        <v>0.05733907509796072</v>
+        <v>0.05670197426353892</v>
       </c>
       <c r="W91">
-        <v>0.2222794460919009</v>
+        <v>0.2224296744686575</v>
       </c>
       <c r="X91" t="inlineStr">
         <is>
@@ -9418,7 +9418,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>0.2783450247473821</v>
+        <v>0.2752523022501889</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -9426,22 +9426,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.2419702414301761</v>
+        <v>0.2438702414301762</v>
       </c>
       <c r="C92">
-        <v>-38.72625407012744</v>
+        <v>-39.76638898389691</v>
       </c>
       <c r="D92">
-        <v>29.65374592987257</v>
+        <v>29.43961101610309</v>
       </c>
       <c r="E92">
-        <v>53.74</v>
+        <v>54.566</v>
       </c>
       <c r="F92">
-        <v>74.34</v>
+        <v>75.166</v>
       </c>
       <c r="G92">
         <v>5.96</v>
@@ -9462,37 +9462,37 @@
         <v>4.824999999999999</v>
       </c>
       <c r="M92">
-        <v>17.529372</v>
+        <v>17.7241428</v>
       </c>
       <c r="N92">
-        <v>-12.704372</v>
+        <v>-12.8991428</v>
       </c>
       <c r="O92">
-        <v>-2.617100632000001</v>
+        <v>-2.6572234168</v>
       </c>
       <c r="P92">
-        <v>-10.087271368</v>
+        <v>-10.2419193832</v>
       </c>
       <c r="Q92">
-        <v>-0.7872713680000007</v>
+        <v>-0.9419193831999984</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>0.4178353440838438</v>
+        <v>0.4591726045376042</v>
       </c>
       <c r="T92">
-        <v>8.592040279072606</v>
+        <v>9.546711421191784</v>
       </c>
       <c r="U92">
         <v>0.2358</v>
       </c>
       <c r="V92">
-        <v>0.05670197426353892</v>
+        <v>0.05607887564525829</v>
       </c>
       <c r="W92">
-        <v>0.2224296744686575</v>
+        <v>0.2225766011228481</v>
       </c>
       <c r="X92" t="inlineStr">
         <is>
@@ -9500,7 +9500,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>0.2752523022501889</v>
+        <v>0.2722275516760111</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -9508,22 +9508,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.2438702414301762</v>
+        <v>0.2457702414301761</v>
       </c>
       <c r="C93">
-        <v>-39.76638898389691</v>
+        <v>-40.8034534581173</v>
       </c>
       <c r="D93">
-        <v>29.43961101610309</v>
+        <v>29.22854654188271</v>
       </c>
       <c r="E93">
-        <v>54.566</v>
+        <v>55.392</v>
       </c>
       <c r="F93">
-        <v>75.166</v>
+        <v>75.992</v>
       </c>
       <c r="G93">
         <v>5.96</v>
@@ -9544,37 +9544,37 @@
         <v>4.824999999999999</v>
       </c>
       <c r="M93">
-        <v>17.7241428</v>
+        <v>17.9189136</v>
       </c>
       <c r="N93">
-        <v>-12.8991428</v>
+        <v>-13.0939136</v>
       </c>
       <c r="O93">
-        <v>-2.6572234168</v>
+        <v>-2.697346201600001</v>
       </c>
       <c r="P93">
-        <v>-10.2419193832</v>
+        <v>-10.3965673984</v>
       </c>
       <c r="Q93">
-        <v>-0.9419193831999984</v>
+        <v>-1.096567398400001</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>0.4591726045376042</v>
+        <v>0.5108441801048049</v>
       </c>
       <c r="T93">
-        <v>9.546711421191784</v>
+        <v>10.74005034884076</v>
       </c>
       <c r="U93">
         <v>0.2358</v>
       </c>
       <c r="V93">
-        <v>0.05607887564525829</v>
+        <v>0.05546932264911415</v>
       </c>
       <c r="W93">
-        <v>0.2225766011228481</v>
+        <v>0.2227203337193389</v>
       </c>
       <c r="X93" t="inlineStr">
         <is>
@@ -9582,7 +9582,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>0.2722275516760111</v>
+        <v>0.2692685565490979</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -9590,22 +9590,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.2457702414301761</v>
+        <v>0.2476702414301761</v>
       </c>
       <c r="C94">
-        <v>-40.8034534581173</v>
+        <v>-41.83751306236143</v>
       </c>
       <c r="D94">
-        <v>29.22854654188271</v>
+        <v>29.02048693763857</v>
       </c>
       <c r="E94">
-        <v>55.392</v>
+        <v>56.218</v>
       </c>
       <c r="F94">
-        <v>75.992</v>
+        <v>76.818</v>
       </c>
       <c r="G94">
         <v>5.96</v>
@@ -9626,37 +9626,37 @@
         <v>4.824999999999999</v>
       </c>
       <c r="M94">
-        <v>17.9189136</v>
+        <v>18.1136844</v>
       </c>
       <c r="N94">
-        <v>-13.0939136</v>
+        <v>-13.2886844</v>
       </c>
       <c r="O94">
-        <v>-2.697346201600001</v>
+        <v>-2.737468986400001</v>
       </c>
       <c r="P94">
-        <v>-10.3965673984</v>
+        <v>-10.5512154136</v>
       </c>
       <c r="Q94">
-        <v>-1.096567398400001</v>
+        <v>-1.251215413600001</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>0.5108441801048049</v>
+        <v>0.5772790629769199</v>
       </c>
       <c r="T94">
-        <v>10.74005034884076</v>
+        <v>12.27434325581801</v>
       </c>
       <c r="U94">
         <v>0.2358</v>
       </c>
       <c r="V94">
-        <v>0.05546932264911415</v>
+        <v>0.05487287831955381</v>
       </c>
       <c r="W94">
-        <v>0.2227203337193389</v>
+        <v>0.2228609752922492</v>
       </c>
       <c r="X94" t="inlineStr">
         <is>
@@ -9664,7 +9664,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>0.2692685565490979</v>
+        <v>0.2663731957259893</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9672,22 +9672,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.2476702414301761</v>
+        <v>0.2495702414301762</v>
       </c>
       <c r="C95">
-        <v>-41.83751306236143</v>
+        <v>-42.86863151240438</v>
       </c>
       <c r="D95">
-        <v>29.02048693763857</v>
+        <v>28.81536848759563</v>
       </c>
       <c r="E95">
-        <v>56.218</v>
+        <v>57.044</v>
       </c>
       <c r="F95">
-        <v>76.818</v>
+        <v>77.64400000000001</v>
       </c>
       <c r="G95">
         <v>5.96</v>
@@ -9708,37 +9708,37 @@
         <v>4.824999999999999</v>
       </c>
       <c r="M95">
-        <v>18.1136844</v>
+        <v>18.3084552</v>
       </c>
       <c r="N95">
-        <v>-13.2886844</v>
+        <v>-13.4834552</v>
       </c>
       <c r="O95">
-        <v>-2.737468986400001</v>
+        <v>-2.7775917712</v>
       </c>
       <c r="P95">
-        <v>-10.5512154136</v>
+        <v>-10.7058634288</v>
       </c>
       <c r="Q95">
-        <v>-1.251215413600001</v>
+        <v>-1.4058634288</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>0.5772790629769199</v>
+        <v>0.6658589068064068</v>
       </c>
       <c r="T95">
-        <v>12.27434325581801</v>
+        <v>14.32006713178769</v>
       </c>
       <c r="U95">
         <v>0.2358</v>
       </c>
       <c r="V95">
-        <v>0.05487287831955381</v>
+        <v>0.05428912429487769</v>
       </c>
       <c r="W95">
-        <v>0.2228609752922492</v>
+        <v>0.2229986244912679</v>
       </c>
       <c r="X95" t="inlineStr">
         <is>
@@ -9746,7 +9746,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>0.2663731957259893</v>
+        <v>0.263539438324649</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9754,22 +9754,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.2495702414301762</v>
+        <v>0.2514702414301762</v>
       </c>
       <c r="C96">
-        <v>-42.86863151240438</v>
+        <v>-43.89687073527714</v>
       </c>
       <c r="D96">
-        <v>28.81536848759563</v>
+        <v>28.61312926472286</v>
       </c>
       <c r="E96">
-        <v>57.044</v>
+        <v>57.87</v>
       </c>
       <c r="F96">
-        <v>77.64400000000001</v>
+        <v>78.47</v>
       </c>
       <c r="G96">
         <v>5.96</v>
@@ -9790,37 +9790,37 @@
         <v>4.824999999999999</v>
       </c>
       <c r="M96">
-        <v>18.3084552</v>
+        <v>18.503226</v>
       </c>
       <c r="N96">
-        <v>-13.4834552</v>
+        <v>-13.678226</v>
       </c>
       <c r="O96">
-        <v>-2.7775917712</v>
+        <v>-2.817714556000001</v>
       </c>
       <c r="P96">
-        <v>-10.7058634288</v>
+        <v>-10.860511444</v>
       </c>
       <c r="Q96">
-        <v>-1.4058634288</v>
+        <v>-1.560511444000001</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>0.6658589068064068</v>
+        <v>0.7898706881676884</v>
       </c>
       <c r="T96">
-        <v>14.32006713178769</v>
+        <v>17.18408055814523</v>
       </c>
       <c r="U96">
         <v>0.2358</v>
       </c>
       <c r="V96">
-        <v>0.05428912429487769</v>
+        <v>0.05371765982861583</v>
       </c>
       <c r="W96">
-        <v>0.2229986244912679</v>
+        <v>0.2231333758124124</v>
       </c>
       <c r="X96" t="inlineStr">
         <is>
@@ -9828,7 +9828,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>0.263539438324649</v>
+        <v>0.2607653389738632</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9836,22 +9836,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.2514702414301762</v>
+        <v>0.2533702414301762</v>
       </c>
       <c r="C97">
-        <v>-43.89687073527714</v>
+        <v>-44.92229093160051</v>
       </c>
       <c r="D97">
-        <v>28.61312926472286</v>
+        <v>28.41370906839949</v>
       </c>
       <c r="E97">
-        <v>57.87</v>
+        <v>58.69600000000001</v>
       </c>
       <c r="F97">
-        <v>78.47</v>
+        <v>79.29600000000001</v>
       </c>
       <c r="G97">
         <v>5.96</v>
@@ -9872,37 +9872,37 @@
         <v>4.824999999999999</v>
       </c>
       <c r="M97">
-        <v>18.503226</v>
+        <v>18.6979968</v>
       </c>
       <c r="N97">
-        <v>-13.678226</v>
+        <v>-13.8729968</v>
       </c>
       <c r="O97">
-        <v>-2.817714556000001</v>
+        <v>-2.857837340800001</v>
       </c>
       <c r="P97">
-        <v>-10.860511444</v>
+        <v>-11.0151594592</v>
       </c>
       <c r="Q97">
-        <v>-1.560511444000001</v>
+        <v>-1.715159459200002</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>0.7898706881676884</v>
+        <v>0.975888360209611</v>
       </c>
       <c r="T97">
-        <v>17.18408055814523</v>
+        <v>21.48010069768155</v>
       </c>
       <c r="U97">
         <v>0.2358</v>
       </c>
       <c r="V97">
-        <v>0.05371765982861583</v>
+        <v>0.05315810087206774</v>
       </c>
       <c r="W97">
-        <v>0.2231333758124124</v>
+        <v>0.2232653198143664</v>
       </c>
       <c r="X97" t="inlineStr">
         <is>
@@ -9910,7 +9910,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>0.2607653389738632</v>
+        <v>0.2580490333595521</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9918,22 +9918,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.2533702414301761</v>
+        <v>0.2552702414301762</v>
       </c>
       <c r="C98">
-        <v>-44.92229093160049</v>
+        <v>-45.94495063532979</v>
       </c>
       <c r="D98">
-        <v>28.4137090683995</v>
+        <v>28.2170493646702</v>
       </c>
       <c r="E98">
-        <v>58.69599999999999</v>
+        <v>59.52199999999998</v>
       </c>
       <c r="F98">
-        <v>79.29599999999999</v>
+        <v>80.12199999999999</v>
       </c>
       <c r="G98">
         <v>5.96</v>
@@ -9954,37 +9954,37 @@
         <v>4.824999999999999</v>
       </c>
       <c r="M98">
-        <v>18.6979968</v>
+        <v>18.8927676</v>
       </c>
       <c r="N98">
-        <v>-13.8729968</v>
+        <v>-14.0677676</v>
       </c>
       <c r="O98">
-        <v>-2.8578373408</v>
+        <v>-2.8979601256</v>
       </c>
       <c r="P98">
-        <v>-11.0151594592</v>
+        <v>-11.1698074744</v>
       </c>
       <c r="Q98">
-        <v>-1.715159459199999</v>
+        <v>-1.869807474399998</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>0.9758883602096085</v>
+        <v>1.285917813612812</v>
       </c>
       <c r="T98">
-        <v>21.48010069768149</v>
+        <v>28.64013426357532</v>
       </c>
       <c r="U98">
         <v>0.2358</v>
       </c>
       <c r="V98">
-        <v>0.05315810087206774</v>
+        <v>0.05261007921359283</v>
       </c>
       <c r="W98">
-        <v>0.2232653198143664</v>
+        <v>0.2233945433214348</v>
       </c>
       <c r="X98" t="inlineStr">
         <is>
@@ -9992,7 +9992,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>0.2580490333595522</v>
+        <v>0.255388734046567</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -10000,22 +10000,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.2552702414301762</v>
+        <v>0.2571702414301761</v>
       </c>
       <c r="C99">
-        <v>-45.94495063532979</v>
+        <v>-46.96490677103598</v>
       </c>
       <c r="D99">
-        <v>28.2170493646702</v>
+        <v>28.02309322896401</v>
       </c>
       <c r="E99">
-        <v>59.52199999999998</v>
+        <v>60.34799999999999</v>
       </c>
       <c r="F99">
-        <v>80.12199999999999</v>
+        <v>80.94799999999999</v>
       </c>
       <c r="G99">
         <v>5.96</v>
@@ -10036,37 +10036,37 @@
         <v>4.824999999999999</v>
       </c>
       <c r="M99">
-        <v>18.8927676</v>
+        <v>19.0875384</v>
       </c>
       <c r="N99">
-        <v>-14.0677676</v>
+        <v>-14.2625384</v>
       </c>
       <c r="O99">
-        <v>-2.8979601256</v>
+        <v>-2.9380829104</v>
       </c>
       <c r="P99">
-        <v>-11.1698074744</v>
+        <v>-11.3244554896</v>
       </c>
       <c r="Q99">
-        <v>-1.869807474399998</v>
+        <v>-2.024455489599999</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>1.285917813612812</v>
+        <v>1.905976720419217</v>
       </c>
       <c r="T99">
-        <v>28.64013426357532</v>
+        <v>42.96020139536298</v>
       </c>
       <c r="U99">
         <v>0.2358</v>
       </c>
       <c r="V99">
-        <v>0.05261007921359283</v>
+        <v>0.05207324167059697</v>
       </c>
       <c r="W99">
-        <v>0.2233945433214348</v>
+        <v>0.2235211296140732</v>
       </c>
       <c r="X99" t="inlineStr">
         <is>
@@ -10074,7 +10074,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>0.255388734046567</v>
+        <v>0.252782726556296</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -10082,22 +10082,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.2571702414301761</v>
+        <v>0.2590702414301762</v>
       </c>
       <c r="C100">
-        <v>-46.96490677103598</v>
+        <v>-47.9822147088403</v>
       </c>
       <c r="D100">
-        <v>28.02309322896401</v>
+        <v>27.83178529115969</v>
       </c>
       <c r="E100">
-        <v>60.34799999999999</v>
+        <v>61.17399999999999</v>
       </c>
       <c r="F100">
-        <v>80.94799999999999</v>
+        <v>81.77399999999999</v>
       </c>
       <c r="G100">
         <v>5.96</v>
@@ -10118,37 +10118,37 @@
         <v>4.824999999999999</v>
       </c>
       <c r="M100">
-        <v>19.0875384</v>
+        <v>19.2823092</v>
       </c>
       <c r="N100">
-        <v>-14.2625384</v>
+        <v>-14.4573092</v>
       </c>
       <c r="O100">
-        <v>-2.9380829104</v>
+        <v>-2.9782056952</v>
       </c>
       <c r="P100">
-        <v>-11.3244554896</v>
+        <v>-11.4791035048</v>
       </c>
       <c r="Q100">
-        <v>-2.024455489599999</v>
+        <v>-2.179103504799997</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>1.905976720419217</v>
+        <v>3.766153440838434</v>
       </c>
       <c r="T100">
-        <v>42.96020139536298</v>
+        <v>85.92040279072596</v>
       </c>
       <c r="U100">
         <v>0.2358</v>
       </c>
       <c r="V100">
-        <v>0.05207324167059697</v>
+        <v>0.05154724933048994</v>
       </c>
       <c r="W100">
-        <v>0.2235211296140732</v>
+        <v>0.2236451586078705</v>
       </c>
       <c r="X100" t="inlineStr">
         <is>
@@ -10156,91 +10156,9 @@
         </is>
       </c>
       <c r="Y100">
-        <v>0.252782726556296</v>
+        <v>0.2502293656819901</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.2590702414301762</v>
-      </c>
-      <c r="C101">
-        <v>-47.9822147088403</v>
-      </c>
-      <c r="D101">
-        <v>27.83178529115969</v>
-      </c>
-      <c r="E101">
-        <v>61.17399999999999</v>
-      </c>
-      <c r="F101">
-        <v>81.77399999999999</v>
-      </c>
-      <c r="G101">
-        <v>5.96</v>
-      </c>
-      <c r="H101">
-        <v>62</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>14.125</v>
-      </c>
-      <c r="K101">
-        <v>9.300000000000001</v>
-      </c>
-      <c r="L101">
-        <v>4.824999999999999</v>
-      </c>
-      <c r="M101">
-        <v>19.2823092</v>
-      </c>
-      <c r="N101">
-        <v>-14.4573092</v>
-      </c>
-      <c r="O101">
-        <v>-2.9782056952</v>
-      </c>
-      <c r="P101">
-        <v>-11.4791035048</v>
-      </c>
-      <c r="Q101">
-        <v>-2.179103504799997</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>3.766153440838434</v>
-      </c>
-      <c r="T101">
-        <v>85.92040279072596</v>
-      </c>
-      <c r="U101">
-        <v>0.2358</v>
-      </c>
-      <c r="V101">
-        <v>0.05154724933048994</v>
-      </c>
-      <c r="W101">
-        <v>0.2236451586078705</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>D2/D</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>0.2502293656819901</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
